--- a/Data Analysis/1_Data/Aggregates/WSA_Winter_all.xlsx
+++ b/Data Analysis/1_Data/Aggregates/WSA_Winter_all.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zg06akex\Documents\Science\05_WP01_MainExperiment\02_Measurements\02_WSA\04_Winter\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mm68tulo\Desktop\Jena Chapter\Data Analysis\1_Data\Aggregates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76EE4A23-EF00-4632-BB31-D691F4AB6817}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A489E3D0-1AE0-4674-9B43-A24CCF65D8F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-16320" yWindow="-120" windowWidth="16440" windowHeight="28440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -39,9 +39,6 @@
     <t>Number</t>
   </si>
   <si>
-    <t>Plot/Subplot/Site</t>
-  </si>
-  <si>
     <t>m sample (g)</t>
   </si>
   <si>
@@ -75,9 +72,6 @@
     <t>m sand + org. rest</t>
   </si>
   <si>
-    <t>Aggregates overall (%)</t>
-  </si>
-  <si>
     <t>Comments</t>
   </si>
   <si>
@@ -619,6 +613,12 @@
   </si>
   <si>
     <t>10.8</t>
+  </si>
+  <si>
+    <t>Plotcode</t>
+  </si>
+  <si>
+    <t>agg_overall</t>
   </si>
 </sst>
 </file>
@@ -659,7 +659,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -938,7 +938,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R241"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="17" max="17" width="10.140625" style="1" bestFit="1" customWidth="1"/>
   </cols>
@@ -948,63 +948,63 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
       <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
+        <v>194</v>
+      </c>
+      <c r="O1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="R1" t="s">
         <v>15</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C2">
         <v>2</v>
@@ -1022,7 +1022,7 @@
         <v>0.48000000000000398</v>
       </c>
       <c r="H2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I2">
         <v>68.790000000000006</v>
@@ -1054,10 +1054,10 @@
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C3">
         <v>2.02</v>
@@ -1075,7 +1075,7 @@
         <v>0.48000000000000398</v>
       </c>
       <c r="H3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I3">
         <v>69.790000000000006</v>
@@ -1104,10 +1104,10 @@
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C4">
         <v>2.0099999999999998</v>
@@ -1125,7 +1125,7 @@
         <v>0.82999999999999829</v>
       </c>
       <c r="H4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I4">
         <v>67.58</v>
@@ -1154,10 +1154,10 @@
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C5">
         <v>2</v>
@@ -1175,7 +1175,7 @@
         <v>0.70000000000000284</v>
       </c>
       <c r="H5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I5">
         <v>68.040000000000006</v>
@@ -1204,10 +1204,10 @@
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C6">
         <v>2.0099999999999998</v>
@@ -1225,7 +1225,7 @@
         <v>0.96999999999999886</v>
       </c>
       <c r="H6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I6">
         <v>67.94</v>
@@ -1254,10 +1254,10 @@
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C7">
         <v>2.0299999999999998</v>
@@ -1275,7 +1275,7 @@
         <v>0.46999999999999886</v>
       </c>
       <c r="H7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I7">
         <v>70.84</v>
@@ -1304,10 +1304,10 @@
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B8" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C8">
         <v>2</v>
@@ -1325,7 +1325,7 @@
         <v>0.53000000000000114</v>
       </c>
       <c r="H8" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I8">
         <v>69.349999999999994</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B9" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C9">
         <v>2</v>
@@ -1375,7 +1375,7 @@
         <v>0.82999999999999829</v>
       </c>
       <c r="H9" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I9">
         <v>69.13</v>
@@ -1404,10 +1404,10 @@
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C10">
         <v>2.02</v>
@@ -1425,7 +1425,7 @@
         <v>0.35000000000000853</v>
       </c>
       <c r="H10" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I10">
         <v>69.72</v>
@@ -1454,10 +1454,10 @@
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C11">
         <v>2.0499999999999998</v>
@@ -1475,7 +1475,7 @@
         <v>0.51000000000000512</v>
       </c>
       <c r="H11" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I11">
         <v>70.47</v>
@@ -1504,10 +1504,10 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C12">
         <v>2.0499999999999998</v>
@@ -1525,7 +1525,7 @@
         <v>0.5</v>
       </c>
       <c r="H12" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I12">
         <v>69.069999999999993</v>
@@ -1554,10 +1554,10 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B13" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C13">
         <v>1.97</v>
@@ -1575,7 +1575,7 @@
         <v>0.68999999999999773</v>
       </c>
       <c r="H13" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I13">
         <v>68.38</v>
@@ -1604,10 +1604,10 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B14" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C14">
         <v>1.99</v>
@@ -1625,7 +1625,7 @@
         <v>0.48000000000000398</v>
       </c>
       <c r="H14" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I14">
         <v>69.75</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B15" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C15">
         <v>2.0099999999999998</v>
@@ -1675,7 +1675,7 @@
         <v>0.63000000000000966</v>
       </c>
       <c r="H15" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I15">
         <v>69.7</v>
@@ -1704,10 +1704,10 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B16" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C16">
         <v>2.02</v>
@@ -1725,7 +1725,7 @@
         <v>0.54000000000000625</v>
       </c>
       <c r="H16" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I16">
         <v>70.02</v>
@@ -1754,10 +1754,10 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B17" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C17">
         <v>2</v>
@@ -1775,7 +1775,7 @@
         <v>0.25999999999999091</v>
       </c>
       <c r="H17" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I17">
         <v>68.59</v>
@@ -1804,10 +1804,10 @@
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C18">
         <v>2</v>
@@ -1825,7 +1825,7 @@
         <v>0.40999999999999659</v>
       </c>
       <c r="H18" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I18">
         <v>70.86</v>
@@ -1854,10 +1854,10 @@
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C19">
         <v>2.0099999999999998</v>
@@ -1875,7 +1875,7 @@
         <v>0.54999999999999716</v>
       </c>
       <c r="H19" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I19">
         <v>69.099999999999994</v>
@@ -1904,10 +1904,10 @@
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B20" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C20">
         <v>2.0099999999999998</v>
@@ -1925,7 +1925,7 @@
         <v>0.18000000000000682</v>
       </c>
       <c r="H20" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I20">
         <v>70.3</v>
@@ -1954,10 +1954,10 @@
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B21" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C21">
         <v>2</v>
@@ -1975,7 +1975,7 @@
         <v>0.65999999999999659</v>
       </c>
       <c r="H21" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I21">
         <v>69.010000000000005</v>
@@ -2004,10 +2004,10 @@
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B22" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C22">
         <v>2.04</v>
@@ -2025,7 +2025,7 @@
         <v>0.69000000000001194</v>
       </c>
       <c r="H22" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I22">
         <v>71.03</v>
@@ -2054,10 +2054,10 @@
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B23" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C23">
         <v>2.02</v>
@@ -2075,7 +2075,7 @@
         <v>0.40000000000000568</v>
       </c>
       <c r="H23" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I23">
         <v>69.64</v>
@@ -2104,10 +2104,10 @@
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B24" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C24">
         <v>1.97</v>
@@ -2125,7 +2125,7 @@
         <v>0.38000000000000966</v>
       </c>
       <c r="H24" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I24">
         <v>70.010000000000005</v>
@@ -2154,10 +2154,10 @@
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B25" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C25">
         <v>2</v>
@@ -2175,7 +2175,7 @@
         <v>0.34000000000000341</v>
       </c>
       <c r="H25" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I25">
         <v>70.930000000000007</v>
@@ -2204,10 +2204,10 @@
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B26" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C26">
         <v>1.99</v>
@@ -2225,7 +2225,7 @@
         <v>0.34000000000000341</v>
       </c>
       <c r="H26" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I26">
         <v>71.11</v>
@@ -2254,10 +2254,10 @@
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B27" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C27">
         <v>2</v>
@@ -2275,7 +2275,7 @@
         <v>0.82999999999999829</v>
       </c>
       <c r="H27" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I27">
         <v>71.22</v>
@@ -2304,10 +2304,10 @@
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B28" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C28">
         <v>2.02</v>
@@ -2325,7 +2325,7 @@
         <v>0.29000000000000625</v>
       </c>
       <c r="H28" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I28">
         <v>71.02</v>
@@ -2354,10 +2354,10 @@
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C29">
         <v>2.0099999999999998</v>
@@ -2375,7 +2375,7 @@
         <v>0.35999999999999943</v>
       </c>
       <c r="H29" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I29">
         <v>69.52</v>
@@ -2404,10 +2404,10 @@
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C30">
         <v>1.99</v>
@@ -2425,7 +2425,7 @@
         <v>0.37000000000000455</v>
       </c>
       <c r="H30" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I30">
         <v>68.209999999999994</v>
@@ -2454,10 +2454,10 @@
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B31" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C31">
         <v>2</v>
@@ -2475,7 +2475,7 @@
         <v>0.61999999999999034</v>
       </c>
       <c r="H31" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I31">
         <v>70.2</v>
@@ -2504,10 +2504,10 @@
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B32" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C32">
         <v>1.98</v>
@@ -2525,7 +2525,7 @@
         <v>0.53000000000000114</v>
       </c>
       <c r="H32" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I32">
         <v>70.040000000000006</v>
@@ -2554,10 +2554,10 @@
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B33" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C33">
         <v>2</v>
@@ -2575,7 +2575,7 @@
         <v>0.36999999999999034</v>
       </c>
       <c r="H33" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I33">
         <v>71.08</v>
@@ -2604,10 +2604,10 @@
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B34" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C34">
         <v>2.0099999999999998</v>
@@ -2625,7 +2625,7 @@
         <v>0.74000000000000909</v>
       </c>
       <c r="H34" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I34">
         <v>72.930000000000007</v>
@@ -2654,10 +2654,10 @@
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B35" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C35">
         <v>2.0299999999999998</v>
@@ -2675,7 +2675,7 @@
         <v>0.37999999999999545</v>
       </c>
       <c r="H35" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I35">
         <v>70.62</v>
@@ -2704,10 +2704,10 @@
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B36" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C36">
         <v>1.99</v>
@@ -2725,7 +2725,7 @@
         <v>0.20999999999999375</v>
       </c>
       <c r="H36" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I36">
         <v>72.05</v>
@@ -2754,10 +2754,10 @@
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B37" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C37">
         <v>2.0299999999999998</v>
@@ -2775,7 +2775,7 @@
         <v>0.25</v>
       </c>
       <c r="H37" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I37">
         <v>71.13</v>
@@ -2804,10 +2804,10 @@
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B38" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C38">
         <v>2</v>
@@ -2825,7 +2825,7 @@
         <v>0.45999999999999375</v>
       </c>
       <c r="H38" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I38">
         <v>69.97</v>
@@ -2854,10 +2854,10 @@
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B39" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C39">
         <v>2.04</v>
@@ -2875,7 +2875,7 @@
         <v>0.24000000000000909</v>
       </c>
       <c r="H39" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I39">
         <v>68.64</v>
@@ -2904,10 +2904,10 @@
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B40" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C40">
         <v>1.99</v>
@@ -2925,7 +2925,7 @@
         <v>0.35000000000000853</v>
       </c>
       <c r="H40" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I40">
         <v>69.95</v>
@@ -2954,10 +2954,10 @@
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B41" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C41">
         <v>2.0499999999999998</v>
@@ -2975,7 +2975,7 @@
         <v>0.59000000000000341</v>
       </c>
       <c r="H41" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I41">
         <v>104.25</v>
@@ -3004,10 +3004,10 @@
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B42" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C42">
         <v>1.98</v>
@@ -3025,7 +3025,7 @@
         <v>0.27000000000001023</v>
       </c>
       <c r="H42" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I42">
         <v>67.569999999999993</v>
@@ -3046,7 +3046,7 @@
         <v>86.174242424243161</v>
       </c>
       <c r="O42" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="P42">
         <v>0.18375</v>
@@ -3060,10 +3060,10 @@
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B43" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C43">
         <v>2</v>
@@ -3081,7 +3081,7 @@
         <v>0.42000000000000171</v>
       </c>
       <c r="H43" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I43">
         <v>71.3</v>
@@ -3110,10 +3110,10 @@
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B44" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C44">
         <v>1.98</v>
@@ -3131,7 +3131,7 @@
         <v>0.20999999999999375</v>
       </c>
       <c r="H44" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I44">
         <v>68.709999999999994</v>
@@ -3160,10 +3160,10 @@
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B45" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C45">
         <v>2</v>
@@ -3181,7 +3181,7 @@
         <v>0.56999999999999318</v>
       </c>
       <c r="H45" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I45">
         <v>70.86</v>
@@ -3210,10 +3210,10 @@
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B46" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C46">
         <v>2.02</v>
@@ -3231,7 +3231,7 @@
         <v>0.32999999999999829</v>
       </c>
       <c r="H46" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I46">
         <v>68.91</v>
@@ -3260,10 +3260,10 @@
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B47" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C47">
         <v>2.04</v>
@@ -3281,7 +3281,7 @@
         <v>1.0700000000000074</v>
       </c>
       <c r="H47" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I47">
         <v>70.47</v>
@@ -3310,10 +3310,10 @@
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B48" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C48">
         <v>2.04</v>
@@ -3331,7 +3331,7 @@
         <v>0.35000000000000853</v>
       </c>
       <c r="H48" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I48">
         <v>70.489999999999995</v>
@@ -3360,10 +3360,10 @@
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B49" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C49">
         <v>2</v>
@@ -3381,7 +3381,7 @@
         <v>0.42999999999999261</v>
       </c>
       <c r="H49" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I49">
         <v>69.180000000000007</v>
@@ -3410,10 +3410,10 @@
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B50" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C50">
         <v>2</v>
@@ -3431,7 +3431,7 @@
         <v>0.71999999999999886</v>
       </c>
       <c r="H50" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I50">
         <v>71.650000000000006</v>
@@ -3460,10 +3460,10 @@
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B51" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C51">
         <v>2</v>
@@ -3481,7 +3481,7 @@
         <v>0.15000000000000568</v>
       </c>
       <c r="H51" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I51">
         <v>69.319999999999993</v>
@@ -3510,10 +3510,10 @@
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B52" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C52">
         <v>2.0099999999999998</v>
@@ -3531,7 +3531,7 @@
         <v>0.45000000000000284</v>
       </c>
       <c r="H52" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I52">
         <v>70.459999999999994</v>
@@ -3560,10 +3560,10 @@
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B53" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C53">
         <v>2.02</v>
@@ -3581,7 +3581,7 @@
         <v>0.14000000000000057</v>
       </c>
       <c r="H53" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I53">
         <v>67.989999999999995</v>
@@ -3610,10 +3610,10 @@
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B54" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C54">
         <v>2</v>
@@ -3631,7 +3631,7 @@
         <v>0.43999999999999773</v>
       </c>
       <c r="H54" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I54">
         <v>69.08</v>
@@ -3660,10 +3660,10 @@
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B55" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C55">
         <v>2.04</v>
@@ -3681,7 +3681,7 @@
         <v>6.9999999999993179E-2</v>
       </c>
       <c r="H55" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I55">
         <v>71.319999999999993</v>
@@ -3710,10 +3710,10 @@
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B56" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C56">
         <v>2.0299999999999998</v>
@@ -3731,7 +3731,7 @@
         <v>0.26999999999999602</v>
       </c>
       <c r="H56" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I56">
         <v>68.61</v>
@@ -3760,10 +3760,10 @@
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B57" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C57">
         <v>1.98</v>
@@ -3781,7 +3781,7 @@
         <v>0.35999999999999943</v>
       </c>
       <c r="H57" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I57">
         <v>69.84</v>
@@ -3810,10 +3810,10 @@
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B58" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C58">
         <v>2.02</v>
@@ -3831,7 +3831,7 @@
         <v>0.32999999999999829</v>
       </c>
       <c r="H58" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I58">
         <v>70.36</v>
@@ -3860,10 +3860,10 @@
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B59" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C59">
         <v>2.04</v>
@@ -3881,7 +3881,7 @@
         <v>0.9100000000000108</v>
       </c>
       <c r="H59" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I59">
         <v>68.040000000000006</v>
@@ -3910,10 +3910,10 @@
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B60" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C60">
         <v>2</v>
@@ -3931,7 +3931,7 @@
         <v>0.50999999999999091</v>
       </c>
       <c r="H60" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I60">
         <v>69.69</v>
@@ -3960,10 +3960,10 @@
     </row>
     <row r="61" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B61" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C61">
         <v>2.0499999999999998</v>
@@ -3981,7 +3981,7 @@
         <v>0.78000000000000114</v>
       </c>
       <c r="H61" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I61">
         <v>71.459999999999994</v>
@@ -4010,10 +4010,10 @@
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B62" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C62">
         <v>2.0099999999999998</v>
@@ -4031,7 +4031,7 @@
         <v>0.46999999999999886</v>
       </c>
       <c r="H62" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I62">
         <v>69.739999999999995</v>
@@ -4060,10 +4060,10 @@
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B63" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C63">
         <v>1.98</v>
@@ -4081,7 +4081,7 @@
         <v>0.28000000000000114</v>
       </c>
       <c r="H63" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I63">
         <v>70.97</v>
@@ -4110,10 +4110,10 @@
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B64" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C64">
         <v>1.98</v>
@@ -4131,7 +4131,7 @@
         <v>0.28000000000000114</v>
       </c>
       <c r="H64" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I64">
         <v>67.91</v>
@@ -4160,10 +4160,10 @@
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B65" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C65">
         <v>1.98</v>
@@ -4181,7 +4181,7 @@
         <v>0.79000000000000625</v>
       </c>
       <c r="H65" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I65">
         <v>70.34</v>
@@ -4210,10 +4210,10 @@
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B66" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C66">
         <v>2.0099999999999998</v>
@@ -4231,7 +4231,7 @@
         <v>0.20999999999999375</v>
       </c>
       <c r="H66" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I66">
         <v>70.02</v>
@@ -4260,10 +4260,10 @@
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B67" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C67">
         <v>2</v>
@@ -4281,7 +4281,7 @@
         <v>0.18999999999999773</v>
       </c>
       <c r="H67" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I67">
         <v>69.64</v>
@@ -4310,10 +4310,10 @@
     </row>
     <row r="68" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B68" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C68">
         <v>2.04</v>
@@ -4331,7 +4331,7 @@
         <v>0.18000000000000682</v>
       </c>
       <c r="H68" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I68">
         <v>70.459999999999994</v>
@@ -4360,10 +4360,10 @@
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B69" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C69">
         <v>2</v>
@@ -4381,7 +4381,7 @@
         <v>0.12000000000000455</v>
       </c>
       <c r="H69" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I69">
         <v>71.38</v>
@@ -4410,10 +4410,10 @@
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B70" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C70">
         <v>1.99</v>
@@ -4431,7 +4431,7 @@
         <v>0.14999999999999147</v>
       </c>
       <c r="H70" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I70">
         <v>69.73</v>
@@ -4460,10 +4460,10 @@
     </row>
     <row r="71" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B71" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C71">
         <v>2.04</v>
@@ -4481,7 +4481,7 @@
         <v>0.34000000000000341</v>
       </c>
       <c r="H71" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I71">
         <v>68.36</v>
@@ -4510,10 +4510,10 @@
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B72" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C72">
         <v>2.04</v>
@@ -4531,7 +4531,7 @@
         <v>0.23000000000000398</v>
       </c>
       <c r="H72" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I72">
         <v>68.59</v>
@@ -4560,10 +4560,10 @@
     </row>
     <row r="73" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B73" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C73">
         <v>2.0099999999999998</v>
@@ -4581,7 +4581,7 @@
         <v>0.43999999999999773</v>
       </c>
       <c r="H73" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I73">
         <v>70.83</v>
@@ -4610,10 +4610,10 @@
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B74" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C74">
         <v>2.0099999999999998</v>
@@ -4631,7 +4631,7 @@
         <v>0.73000000000000398</v>
       </c>
       <c r="H74" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I74">
         <v>71.23</v>
@@ -4660,10 +4660,10 @@
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B75" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C75">
         <v>2.0099999999999998</v>
@@ -4681,7 +4681,7 @@
         <v>0.31000000000000227</v>
       </c>
       <c r="H75" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I75">
         <v>71.459999999999994</v>
@@ -4710,10 +4710,10 @@
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B76" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C76">
         <v>1.97</v>
@@ -4731,7 +4731,7 @@
         <v>0.40999999999999659</v>
       </c>
       <c r="H76" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I76">
         <v>69.13</v>
@@ -4760,10 +4760,10 @@
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B77" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C77">
         <v>1.95</v>
@@ -4781,7 +4781,7 @@
         <v>0.28999999999999204</v>
       </c>
       <c r="H77" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I77">
         <v>70.290000000000006</v>
@@ -4810,10 +4810,10 @@
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B78" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C78">
         <v>2.0299999999999998</v>
@@ -4831,7 +4831,7 @@
         <v>0.59000000000000341</v>
       </c>
       <c r="H78" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I78">
         <v>69.209999999999994</v>
@@ -4860,10 +4860,10 @@
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B79" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C79">
         <v>1.98</v>
@@ -4881,7 +4881,7 @@
         <v>0.58000000000001251</v>
       </c>
       <c r="H79" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I79">
         <v>68.59</v>
@@ -4910,10 +4910,10 @@
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B80" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C80">
         <v>2.02</v>
@@ -4931,7 +4931,7 @@
         <v>0.68000000000000682</v>
       </c>
       <c r="H80" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I80">
         <v>69.62</v>
@@ -4960,10 +4960,10 @@
     </row>
     <row r="81" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B81" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C81">
         <v>1.98</v>
@@ -4981,7 +4981,7 @@
         <v>0.20999999999999375</v>
       </c>
       <c r="H81" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I81">
         <v>69.569999999999993</v>
@@ -5010,10 +5010,10 @@
     </row>
     <row r="82" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B82" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C82">
         <v>1.98</v>
@@ -5031,7 +5031,7 @@
         <v>0.21999999999999886</v>
       </c>
       <c r="H82" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I82">
         <v>67.91</v>
@@ -5063,10 +5063,10 @@
     </row>
     <row r="83" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B83" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C83">
         <v>2</v>
@@ -5084,7 +5084,7 @@
         <v>0.57999999999999829</v>
       </c>
       <c r="H83" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I83">
         <v>67.94</v>
@@ -5113,10 +5113,10 @@
     </row>
     <row r="84" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B84" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C84">
         <v>1.99</v>
@@ -5134,7 +5134,7 @@
         <v>0.32999999999999829</v>
       </c>
       <c r="H84" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I84">
         <v>67.89</v>
@@ -5163,10 +5163,10 @@
     </row>
     <row r="85" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B85" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C85">
         <v>2</v>
@@ -5184,7 +5184,7 @@
         <v>0.75</v>
       </c>
       <c r="H85" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I85">
         <v>69.02</v>
@@ -5213,10 +5213,10 @@
     </row>
     <row r="86" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B86" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C86">
         <v>1.97</v>
@@ -5234,7 +5234,7 @@
         <v>0.22000000000001307</v>
       </c>
       <c r="H86" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I86">
         <v>69.16</v>
@@ -5263,10 +5263,10 @@
     </row>
     <row r="87" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B87" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C87">
         <v>1.98</v>
@@ -5284,7 +5284,7 @@
         <v>0.85000000000000853</v>
       </c>
       <c r="H87" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I87">
         <v>68.78</v>
@@ -5313,10 +5313,10 @@
     </row>
     <row r="88" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B88" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C88">
         <v>2.0499999999999998</v>
@@ -5334,7 +5334,7 @@
         <v>0.34000000000000341</v>
       </c>
       <c r="H88" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I88">
         <v>70.349999999999994</v>
@@ -5363,10 +5363,10 @@
     </row>
     <row r="89" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B89" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C89">
         <v>2.0099999999999998</v>
@@ -5384,7 +5384,7 @@
         <v>0.17999999999999261</v>
       </c>
       <c r="H89" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I89">
         <v>69.84</v>
@@ -5413,10 +5413,10 @@
     </row>
     <row r="90" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B90" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C90">
         <v>2.0299999999999998</v>
@@ -5434,7 +5434,7 @@
         <v>0.15999999999999659</v>
       </c>
       <c r="H90" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I90">
         <v>69.55</v>
@@ -5463,10 +5463,10 @@
     </row>
     <row r="91" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B91" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C91">
         <v>2.04</v>
@@ -5484,7 +5484,7 @@
         <v>0.33000000000001251</v>
       </c>
       <c r="H91" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I91">
         <v>70.58</v>
@@ -5513,10 +5513,10 @@
     </row>
     <row r="92" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B92" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C92">
         <v>2</v>
@@ -5534,7 +5534,7 @@
         <v>0.18000000000000682</v>
       </c>
       <c r="H92" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I92">
         <v>70.98</v>
@@ -5563,10 +5563,10 @@
     </row>
     <row r="93" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B93" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C93">
         <v>2.0499999999999998</v>
@@ -5584,7 +5584,7 @@
         <v>0.21999999999999886</v>
       </c>
       <c r="H93" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I93">
         <v>68.72</v>
@@ -5613,10 +5613,10 @@
     </row>
     <row r="94" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B94" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C94">
         <v>2</v>
@@ -5634,7 +5634,7 @@
         <v>0.28999999999999204</v>
       </c>
       <c r="H94" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I94">
         <v>69.13</v>
@@ -5663,10 +5663,10 @@
     </row>
     <row r="95" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B95" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C95">
         <v>2.04</v>
@@ -5684,7 +5684,7 @@
         <v>0.50999999999999091</v>
       </c>
       <c r="H95" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I95">
         <v>71.3</v>
@@ -5713,10 +5713,10 @@
     </row>
     <row r="96" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B96" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C96">
         <v>2.0299999999999998</v>
@@ -5734,7 +5734,7 @@
         <v>0.5</v>
       </c>
       <c r="H96" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I96">
         <v>69.64</v>
@@ -5763,10 +5763,10 @@
     </row>
     <row r="97" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B97" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C97">
         <v>2.0099999999999998</v>
@@ -5784,7 +5784,7 @@
         <v>4.9999999999997158E-2</v>
       </c>
       <c r="H97" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I97">
         <v>69.72</v>
@@ -5813,10 +5813,10 @@
     </row>
     <row r="98" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B98" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C98">
         <v>1.99</v>
@@ -5834,7 +5834,7 @@
         <v>0.57000000000000739</v>
       </c>
       <c r="H98" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I98">
         <v>68.73</v>
@@ -5863,10 +5863,10 @@
     </row>
     <row r="99" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B99" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C99">
         <v>2.02</v>
@@ -5884,7 +5884,7 @@
         <v>0.29000000000000625</v>
       </c>
       <c r="H99" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I99">
         <v>68.959999999999994</v>
@@ -5913,10 +5913,10 @@
     </row>
     <row r="100" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B100" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C100">
         <v>2.0099999999999998</v>
@@ -5934,7 +5934,7 @@
         <v>0.17000000000000171</v>
       </c>
       <c r="H100" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I100">
         <v>71.03</v>
@@ -5963,10 +5963,10 @@
     </row>
     <row r="101" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B101" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C101">
         <v>2.0099999999999998</v>
@@ -5984,7 +5984,7 @@
         <v>0.42999999999999261</v>
       </c>
       <c r="H101" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I101">
         <v>68.64</v>
@@ -6013,10 +6013,10 @@
     </row>
     <row r="102" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B102" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C102">
         <v>2</v>
@@ -6034,7 +6034,7 @@
         <v>0.51000000000000512</v>
       </c>
       <c r="H102" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I102">
         <v>69.900000000000006</v>
@@ -6063,10 +6063,10 @@
     </row>
     <row r="103" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B103" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C103">
         <v>2.0499999999999998</v>
@@ -6084,7 +6084,7 @@
         <v>0.50999999999999091</v>
       </c>
       <c r="H103" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I103">
         <v>69.17</v>
@@ -6113,10 +6113,10 @@
     </row>
     <row r="104" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B104" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C104">
         <v>2</v>
@@ -6134,7 +6134,7 @@
         <v>9.9999999999994316E-2</v>
       </c>
       <c r="H104" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I104">
         <v>70.709999999999994</v>
@@ -6163,10 +6163,10 @@
     </row>
     <row r="105" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B105" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C105">
         <v>1.99</v>
@@ -6184,7 +6184,7 @@
         <v>0.53000000000000114</v>
       </c>
       <c r="H105" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I105">
         <v>67.989999999999995</v>
@@ -6213,10 +6213,10 @@
     </row>
     <row r="106" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B106" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C106">
         <v>2</v>
@@ -6234,7 +6234,7 @@
         <v>0.10000000000000853</v>
       </c>
       <c r="H106" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I106">
         <v>69.95</v>
@@ -6263,10 +6263,10 @@
     </row>
     <row r="107" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B107" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C107">
         <v>1.98</v>
@@ -6284,7 +6284,7 @@
         <v>0.79999999999999716</v>
       </c>
       <c r="H107" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I107">
         <v>68.08</v>
@@ -6313,10 +6313,10 @@
     </row>
     <row r="108" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B108" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C108">
         <v>2.0299999999999998</v>
@@ -6334,7 +6334,7 @@
         <v>0.19000000000001194</v>
       </c>
       <c r="H108" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I108">
         <v>68.58</v>
@@ -6363,10 +6363,10 @@
     </row>
     <row r="109" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B109" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C109">
         <v>1.97</v>
@@ -6384,7 +6384,7 @@
         <v>0.72999999999998977</v>
       </c>
       <c r="H109" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I109">
         <v>71.28</v>
@@ -6413,10 +6413,10 @@
     </row>
     <row r="110" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B110" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C110">
         <v>1.99</v>
@@ -6434,7 +6434,7 @@
         <v>0.34000000000000341</v>
       </c>
       <c r="H110" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I110">
         <v>69.760000000000005</v>
@@ -6463,10 +6463,10 @@
     </row>
     <row r="111" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B111" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C111">
         <v>1.98</v>
@@ -6484,7 +6484,7 @@
         <v>0.82000000000000739</v>
       </c>
       <c r="H111" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I111">
         <v>70.849999999999994</v>
@@ -6513,10 +6513,10 @@
     </row>
     <row r="112" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B112" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C112">
         <v>1.99</v>
@@ -6534,7 +6534,7 @@
         <v>0.57999999999999829</v>
       </c>
       <c r="H112" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I112">
         <v>71.08</v>
@@ -6563,10 +6563,10 @@
     </row>
     <row r="113" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B113" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C113">
         <v>2</v>
@@ -6584,7 +6584,7 @@
         <v>0.73000000000000398</v>
       </c>
       <c r="H113" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I113">
         <v>68.56</v>
@@ -6613,10 +6613,10 @@
     </row>
     <row r="114" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B114" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C114">
         <v>2</v>
@@ -6634,7 +6634,7 @@
         <v>0.5899999999999892</v>
       </c>
       <c r="H114" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I114">
         <v>70.19</v>
@@ -6663,10 +6663,10 @@
     </row>
     <row r="115" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B115" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C115">
         <v>2.02</v>
@@ -6684,7 +6684,7 @@
         <v>0.40000000000000568</v>
       </c>
       <c r="H115" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I115">
         <v>69.38</v>
@@ -6713,10 +6713,10 @@
     </row>
     <row r="116" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B116" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C116">
         <v>2.02</v>
@@ -6734,7 +6734,7 @@
         <v>0.67000000000000171</v>
       </c>
       <c r="H116" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I116">
         <v>69.58</v>
@@ -6763,10 +6763,10 @@
     </row>
     <row r="117" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B117" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C117">
         <v>2.04</v>
@@ -6784,7 +6784,7 @@
         <v>0.29000000000000625</v>
       </c>
       <c r="H117" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I117">
         <v>70.16</v>
@@ -6813,10 +6813,10 @@
     </row>
     <row r="118" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B118" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C118">
         <v>2.02</v>
@@ -6834,7 +6834,7 @@
         <v>0.32000000000000739</v>
       </c>
       <c r="H118" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I118">
         <v>70.459999999999994</v>
@@ -6863,10 +6863,10 @@
     </row>
     <row r="119" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B119" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C119">
         <v>2.0099999999999998</v>
@@ -6884,7 +6884,7 @@
         <v>0.26999999999999602</v>
       </c>
       <c r="H119" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I119">
         <v>69.25</v>
@@ -6913,10 +6913,10 @@
     </row>
     <row r="120" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B120" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C120">
         <v>2.04</v>
@@ -6934,7 +6934,7 @@
         <v>0.68999999999999773</v>
       </c>
       <c r="H120" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I120">
         <v>70.099999999999994</v>
@@ -6963,10 +6963,10 @@
     </row>
     <row r="121" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B121" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C121">
         <v>2.0299999999999998</v>
@@ -6984,7 +6984,7 @@
         <v>0.73999999999999488</v>
       </c>
       <c r="H121" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I121">
         <v>71.06</v>
@@ -7013,10 +7013,10 @@
     </row>
     <row r="122" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B122" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C122">
         <v>2.0099999999999998</v>
@@ -7034,7 +7034,7 @@
         <v>0.35000000000000142</v>
       </c>
       <c r="H122" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I122">
         <v>70.31</v>
@@ -7066,10 +7066,10 @@
     </row>
     <row r="123" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B123" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C123">
         <v>2.0099999999999998</v>
@@ -7087,7 +7087,7 @@
         <v>0.64999999999999858</v>
       </c>
       <c r="H123" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I123">
         <v>70.2</v>
@@ -7116,10 +7116,10 @@
     </row>
     <row r="124" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B124" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C124">
         <v>2.02</v>
@@ -7137,7 +7137,7 @@
         <v>0.34999999999999432</v>
       </c>
       <c r="H124" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I124">
         <v>69.39</v>
@@ -7166,10 +7166,10 @@
     </row>
     <row r="125" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B125" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C125">
         <v>2</v>
@@ -7187,7 +7187,7 @@
         <v>0.20000000000000284</v>
       </c>
       <c r="H125" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I125">
         <v>71.069999999999993</v>
@@ -7216,10 +7216,10 @@
     </row>
     <row r="126" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B126" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C126">
         <v>2</v>
@@ -7237,7 +7237,7 @@
         <v>0.51000000000000512</v>
       </c>
       <c r="H126" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I126">
         <v>70.23</v>
@@ -7266,10 +7266,10 @@
     </row>
     <row r="127" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B127" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C127">
         <v>1.97</v>
@@ -7287,7 +7287,7 @@
         <v>0.42999999999999972</v>
       </c>
       <c r="H127" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I127">
         <v>69.62</v>
@@ -7316,10 +7316,10 @@
     </row>
     <row r="128" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B128" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C128">
         <v>2.0299999999999998</v>
@@ -7337,7 +7337,7 @@
         <v>0.38000000000000256</v>
       </c>
       <c r="H128" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I128">
         <v>73.260000000000005</v>
@@ -7366,10 +7366,10 @@
     </row>
     <row r="129" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B129" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C129">
         <v>2.02</v>
@@ -7387,7 +7387,7 @@
         <v>0.74000000000000199</v>
       </c>
       <c r="H129" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I129">
         <v>68.55</v>
@@ -7416,10 +7416,10 @@
     </row>
     <row r="130" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B130" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C130">
         <v>2</v>
@@ -7437,7 +7437,7 @@
         <v>0.35000000000000142</v>
       </c>
       <c r="H130" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I130">
         <v>69.78</v>
@@ -7466,10 +7466,10 @@
     </row>
     <row r="131" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B131" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C131">
         <v>1.96</v>
@@ -7487,7 +7487,7 @@
         <v>1.009999999999998</v>
       </c>
       <c r="H131" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I131">
         <v>71.86</v>
@@ -7516,10 +7516,10 @@
     </row>
     <row r="132" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B132" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C132">
         <v>1.99</v>
@@ -7537,7 +7537,7 @@
         <v>0.24000000000000199</v>
       </c>
       <c r="H132" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I132">
         <v>70.23</v>
@@ -7566,10 +7566,10 @@
     </row>
     <row r="133" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B133" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C133">
         <v>2.02</v>
@@ -7587,7 +7587,7 @@
         <v>0.40999999999999659</v>
       </c>
       <c r="H133" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I133">
         <v>68.099999999999994</v>
@@ -7616,10 +7616,10 @@
     </row>
     <row r="134" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B134" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C134">
         <v>2.04</v>
@@ -7637,7 +7637,7 @@
         <v>0.31000000000000227</v>
       </c>
       <c r="H134" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I134">
         <v>69.349999999999994</v>
@@ -7666,10 +7666,10 @@
     </row>
     <row r="135" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B135" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C135">
         <v>2.0099999999999998</v>
@@ -7687,7 +7687,7 @@
         <v>0.36999999999999744</v>
       </c>
       <c r="H135" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I135">
         <v>69.05</v>
@@ -7716,10 +7716,10 @@
     </row>
     <row r="136" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B136" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C136">
         <v>2.0099999999999998</v>
@@ -7737,7 +7737,7 @@
         <v>0.14000000000000057</v>
       </c>
       <c r="H136" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I136">
         <v>69.7</v>
@@ -7766,10 +7766,10 @@
     </row>
     <row r="137" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B137" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C137">
         <v>2.0299999999999998</v>
@@ -7787,7 +7787,7 @@
         <v>0.39000000000000057</v>
       </c>
       <c r="H137" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I137">
         <v>70.040000000000006</v>
@@ -7816,10 +7816,10 @@
     </row>
     <row r="138" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B138" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C138">
         <v>1.98</v>
@@ -7837,7 +7837,7 @@
         <v>0.68999999999999773</v>
       </c>
       <c r="H138" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I138">
         <v>68.069999999999993</v>
@@ -7866,10 +7866,10 @@
     </row>
     <row r="139" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B139" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C139">
         <v>1.96</v>
@@ -7887,7 +7887,7 @@
         <v>0.36999999999999744</v>
       </c>
       <c r="H139" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I139">
         <v>69.66</v>
@@ -7916,10 +7916,10 @@
     </row>
     <row r="140" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B140" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C140">
         <v>1.98</v>
@@ -7937,7 +7937,7 @@
         <v>0.32000000000000028</v>
       </c>
       <c r="H140" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I140">
         <v>70.06</v>
@@ -7966,10 +7966,10 @@
     </row>
     <row r="141" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B141" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C141">
         <v>2</v>
@@ -7987,7 +7987,7 @@
         <v>0.64000000000000057</v>
       </c>
       <c r="H141" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I141">
         <v>69.83</v>
@@ -8016,10 +8016,10 @@
     </row>
     <row r="142" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B142" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C142">
         <v>2.04</v>
@@ -8037,7 +8037,7 @@
         <v>0.54999999999999716</v>
       </c>
       <c r="H142" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I142">
         <v>70.739999999999995</v>
@@ -8066,10 +8066,10 @@
     </row>
     <row r="143" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B143" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C143">
         <v>2.0299999999999998</v>
@@ -8087,7 +8087,7 @@
         <v>0.74000000000000199</v>
       </c>
       <c r="H143" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I143">
         <v>69.11</v>
@@ -8116,10 +8116,10 @@
     </row>
     <row r="144" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B144" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C144">
         <v>1.95</v>
@@ -8137,7 +8137,7 @@
         <v>0.31000000000000227</v>
       </c>
       <c r="H144" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I144">
         <v>71.12</v>
@@ -8166,10 +8166,10 @@
     </row>
     <row r="145" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B145" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C145">
         <v>2.0499999999999998</v>
@@ -8187,7 +8187,7 @@
         <v>0.50999999999999801</v>
       </c>
       <c r="H145" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I145">
         <v>68.680000000000007</v>
@@ -8216,10 +8216,10 @@
     </row>
     <row r="146" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B146" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C146">
         <v>2.04</v>
@@ -8237,7 +8237,7 @@
         <v>0.82999999999999829</v>
       </c>
       <c r="H146" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I146">
         <v>68.5</v>
@@ -8266,10 +8266,10 @@
     </row>
     <row r="147" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B147" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C147">
         <v>2</v>
@@ -8287,7 +8287,7 @@
         <v>0.56000000000000227</v>
       </c>
       <c r="H147" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I147">
         <v>70.78</v>
@@ -8316,10 +8316,10 @@
     </row>
     <row r="148" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B148" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C148">
         <v>1.99</v>
@@ -8337,7 +8337,7 @@
         <v>0.28999999999999915</v>
       </c>
       <c r="H148" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I148">
         <v>68.7</v>
@@ -8366,10 +8366,10 @@
     </row>
     <row r="149" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B149" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C149">
         <v>2.04</v>
@@ -8387,7 +8387,7 @@
         <v>0.63999999999999346</v>
       </c>
       <c r="H149" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I149">
         <v>69.069999999999993</v>
@@ -8416,10 +8416,10 @@
     </row>
     <row r="150" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B150" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C150">
         <v>2.0299999999999998</v>
@@ -8437,7 +8437,7 @@
         <v>0.67999999999999972</v>
       </c>
       <c r="H150" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I150">
         <v>70.66</v>
@@ -8466,10 +8466,10 @@
     </row>
     <row r="151" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B151" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C151">
         <v>1.95</v>
@@ -8487,7 +8487,7 @@
         <v>0.81000000000000227</v>
       </c>
       <c r="H151" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I151">
         <v>69.19</v>
@@ -8516,10 +8516,10 @@
     </row>
     <row r="152" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B152" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C152">
         <v>2.02</v>
@@ -8537,7 +8537,7 @@
         <v>0.25</v>
       </c>
       <c r="H152" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I152">
         <v>68.61</v>
@@ -8566,10 +8566,10 @@
     </row>
     <row r="153" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B153" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C153">
         <v>1.97</v>
@@ -8587,7 +8587,7 @@
         <v>0.38999999999999346</v>
       </c>
       <c r="H153" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I153">
         <v>68.489999999999995</v>
@@ -8616,10 +8616,10 @@
     </row>
     <row r="154" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B154" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C154">
         <v>2</v>
@@ -8637,7 +8637,7 @@
         <v>9.9999999999994316E-2</v>
       </c>
       <c r="H154" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I154">
         <v>71.03</v>
@@ -8666,10 +8666,10 @@
     </row>
     <row r="155" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B155" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C155">
         <v>2</v>
@@ -8687,7 +8687,7 @@
         <v>0.52000000000000313</v>
       </c>
       <c r="H155" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I155">
         <v>69.12</v>
@@ -8716,10 +8716,10 @@
     </row>
     <row r="156" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B156" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C156">
         <v>1.96</v>
@@ -8737,7 +8737,7 @@
         <v>0.42000000000000171</v>
       </c>
       <c r="H156" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I156">
         <v>70.66</v>
@@ -8766,10 +8766,10 @@
     </row>
     <row r="157" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B157" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C157">
         <v>1.99</v>
@@ -8787,7 +8787,7 @@
         <v>0.36999999999999744</v>
       </c>
       <c r="H157" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I157">
         <v>68.599999999999994</v>
@@ -8816,10 +8816,10 @@
     </row>
     <row r="158" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B158" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C158">
         <v>1.95</v>
@@ -8837,7 +8837,7 @@
         <v>0.46000000000000085</v>
       </c>
       <c r="H158" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I158">
         <v>69.89</v>
@@ -8866,10 +8866,10 @@
     </row>
     <row r="159" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B159" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C159">
         <v>2.0499999999999998</v>
@@ -8887,7 +8887,7 @@
         <v>0.50999999999999801</v>
       </c>
       <c r="H159" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I159">
         <v>70.56</v>
@@ -8916,10 +8916,10 @@
     </row>
     <row r="160" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B160" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C160">
         <v>2</v>
@@ -8937,7 +8937,7 @@
         <v>0.78999999999999915</v>
       </c>
       <c r="H160" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I160">
         <v>69.989999999999995</v>
@@ -8966,10 +8966,10 @@
     </row>
     <row r="161" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B161" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C161">
         <v>1.99</v>
@@ -8987,7 +8987,7 @@
         <v>0.39999999999999858</v>
       </c>
       <c r="H161" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I161">
         <v>70.88</v>
@@ -9016,10 +9016,10 @@
     </row>
     <row r="162" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B162" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C162">
         <v>2.04</v>
@@ -9037,7 +9037,7 @@
         <v>0.32999999999999829</v>
       </c>
       <c r="H162" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I162">
         <v>69.44</v>
@@ -9069,10 +9069,10 @@
     </row>
     <row r="163" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B163" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C163">
         <v>1.99</v>
@@ -9090,7 +9090,7 @@
         <v>0.48000000000000398</v>
       </c>
       <c r="H163" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I163">
         <v>69.260000000000005</v>
@@ -9119,10 +9119,10 @@
     </row>
     <row r="164" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B164" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C164">
         <v>2.0099999999999998</v>
@@ -9140,7 +9140,7 @@
         <v>0.48999999999999488</v>
       </c>
       <c r="H164" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I164">
         <v>69.77</v>
@@ -9169,10 +9169,10 @@
     </row>
     <row r="165" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B165" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C165">
         <v>2.0099999999999998</v>
@@ -9190,7 +9190,7 @@
         <v>0.95000000000000284</v>
       </c>
       <c r="H165" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I165">
         <v>69.77</v>
@@ -9219,10 +9219,10 @@
     </row>
     <row r="166" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B166" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C166">
         <v>1.96</v>
@@ -9240,7 +9240,7 @@
         <v>0.46000000000000085</v>
       </c>
       <c r="H166" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I166">
         <v>70</v>
@@ -9269,10 +9269,10 @@
     </row>
     <row r="167" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B167" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C167">
         <v>2</v>
@@ -9290,7 +9290,7 @@
         <v>0.24000000000000199</v>
       </c>
       <c r="H167" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I167">
         <v>71.319999999999993</v>
@@ -9319,10 +9319,10 @@
     </row>
     <row r="168" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B168" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C168">
         <v>2</v>
@@ -9340,7 +9340,7 @@
         <v>0.23000000000000398</v>
       </c>
       <c r="H168" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I168">
         <v>69.13</v>
@@ -9369,10 +9369,10 @@
     </row>
     <row r="169" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B169" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C169">
         <v>1.97</v>
@@ -9390,7 +9390,7 @@
         <v>0.57000000000000028</v>
       </c>
       <c r="H169" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I169">
         <v>71.37</v>
@@ -9419,10 +9419,10 @@
     </row>
     <row r="170" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B170" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C170">
         <v>2.0299999999999998</v>
@@ -9440,7 +9440,7 @@
         <v>0.96000000000000085</v>
       </c>
       <c r="H170" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I170">
         <v>70.010000000000005</v>
@@ -9469,10 +9469,10 @@
     </row>
     <row r="171" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B171" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C171">
         <v>1.99</v>
@@ -9490,7 +9490,7 @@
         <v>0.60000000000000142</v>
       </c>
       <c r="H171" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I171">
         <v>70.19</v>
@@ -9519,10 +9519,10 @@
     </row>
     <row r="172" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B172" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C172">
         <v>1.98</v>
@@ -9540,7 +9540,7 @@
         <v>0.16000000000000369</v>
       </c>
       <c r="H172" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I172">
         <v>71.08</v>
@@ -9569,10 +9569,10 @@
     </row>
     <row r="173" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B173" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C173">
         <v>2.04</v>
@@ -9590,7 +9590,7 @@
         <v>0.13000000000000256</v>
       </c>
       <c r="H173" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I173">
         <v>70.84</v>
@@ -9619,10 +9619,10 @@
     </row>
     <row r="174" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B174" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C174">
         <v>2.02</v>
@@ -9640,7 +9640,7 @@
         <v>0.37999999999999545</v>
       </c>
       <c r="H174" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I174">
         <v>70.58</v>
@@ -9669,10 +9669,10 @@
     </row>
     <row r="175" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B175" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C175">
         <v>2</v>
@@ -9690,7 +9690,7 @@
         <v>0.26999999999999602</v>
       </c>
       <c r="H175" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I175">
         <v>70.48</v>
@@ -9719,10 +9719,10 @@
     </row>
     <row r="176" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B176" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C176">
         <v>2.02</v>
@@ -9740,7 +9740,7 @@
         <v>0.19999999999999574</v>
       </c>
       <c r="H176" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I176">
         <v>69.23</v>
@@ -9769,10 +9769,10 @@
     </row>
     <row r="177" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B177" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C177">
         <v>2.02</v>
@@ -9790,7 +9790,7 @@
         <v>0.51999999999999602</v>
       </c>
       <c r="H177" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I177">
         <v>71.05</v>
@@ -9819,10 +9819,10 @@
     </row>
     <row r="178" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B178" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C178">
         <v>2.0099999999999998</v>
@@ -9840,7 +9840,7 @@
         <v>0.55999999999999517</v>
       </c>
       <c r="H178" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I178">
         <v>69.099999999999994</v>
@@ -9869,10 +9869,10 @@
     </row>
     <row r="179" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B179" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C179">
         <v>2.0499999999999998</v>
@@ -9890,7 +9890,7 @@
         <v>0.93999999999999773</v>
       </c>
       <c r="H179" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I179">
         <v>68.739999999999995</v>
@@ -9919,10 +9919,10 @@
     </row>
     <row r="180" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B180" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C180">
         <v>2.0499999999999998</v>
@@ -9940,7 +9940,7 @@
         <v>0.3300000000000054</v>
       </c>
       <c r="H180" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I180">
         <v>71.28</v>
@@ -9969,10 +9969,10 @@
     </row>
     <row r="181" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B181" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C181">
         <v>1.98</v>
@@ -9990,7 +9990,7 @@
         <v>0.16000000000000369</v>
       </c>
       <c r="H181" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I181">
         <v>70.16</v>
@@ -10019,10 +10019,10 @@
     </row>
     <row r="182" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B182" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C182">
         <v>2.0299999999999998</v>
@@ -10040,7 +10040,7 @@
         <v>0.35999999999999943</v>
       </c>
       <c r="H182" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I182">
         <v>70.27</v>
@@ -10069,10 +10069,10 @@
     </row>
     <row r="183" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B183" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C183">
         <v>1.97</v>
@@ -10090,7 +10090,7 @@
         <v>0.20000000000000284</v>
       </c>
       <c r="H183" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I183">
         <v>71.19</v>
@@ -10119,10 +10119,10 @@
     </row>
     <row r="184" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B184" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C184">
         <v>2.0499999999999998</v>
@@ -10140,7 +10140,7 @@
         <v>0.34000000000000341</v>
       </c>
       <c r="H184" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I184">
         <v>68.59</v>
@@ -10169,10 +10169,10 @@
     </row>
     <row r="185" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B185" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C185">
         <v>1.98</v>
@@ -10190,7 +10190,7 @@
         <v>0.34999999999999432</v>
       </c>
       <c r="H185" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I185">
         <v>70</v>
@@ -10219,10 +10219,10 @@
     </row>
     <row r="186" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B186" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C186">
         <v>2.0099999999999998</v>
@@ -10240,7 +10240,7 @@
         <v>0.64000000000000057</v>
       </c>
       <c r="H186" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I186">
         <v>70.11</v>
@@ -10269,10 +10269,10 @@
     </row>
     <row r="187" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B187" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C187">
         <v>1.97</v>
@@ -10290,7 +10290,7 @@
         <v>0.17000000000000171</v>
       </c>
       <c r="H187" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I187">
         <v>69.67</v>
@@ -10319,10 +10319,10 @@
     </row>
     <row r="188" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B188" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C188">
         <v>2.02</v>
@@ -10340,7 +10340,7 @@
         <v>0.26000000000000512</v>
       </c>
       <c r="H188" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I188">
         <v>69.97</v>
@@ -10369,10 +10369,10 @@
     </row>
     <row r="189" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B189" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C189">
         <v>1.98</v>
@@ -10390,7 +10390,7 @@
         <v>0.59000000000000341</v>
       </c>
       <c r="H189" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I189">
         <v>69.09</v>
@@ -10419,10 +10419,10 @@
     </row>
     <row r="190" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B190" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C190">
         <v>2.0099999999999998</v>
@@ -10440,7 +10440,7 @@
         <v>0.42999999999999972</v>
       </c>
       <c r="H190" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I190">
         <v>70.44</v>
@@ -10469,10 +10469,10 @@
     </row>
     <row r="191" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B191" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C191">
         <v>1.97</v>
@@ -10490,7 +10490,7 @@
         <v>0.12000000000000455</v>
       </c>
       <c r="H191" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I191">
         <v>70.900000000000006</v>
@@ -10519,10 +10519,10 @@
     </row>
     <row r="192" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B192" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C192">
         <v>1.97</v>
@@ -10540,7 +10540,7 @@
         <v>0.47000000000000597</v>
       </c>
       <c r="H192" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I192">
         <v>68.87</v>
@@ -10569,10 +10569,10 @@
     </row>
     <row r="193" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B193" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C193">
         <v>2.0299999999999998</v>
@@ -10590,7 +10590,7 @@
         <v>0.60999999999999943</v>
       </c>
       <c r="H193" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I193">
         <v>68.56</v>
@@ -10619,10 +10619,10 @@
     </row>
     <row r="194" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B194" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C194">
         <v>2.04</v>
@@ -10640,7 +10640,7 @@
         <v>0.39000000000000057</v>
       </c>
       <c r="H194" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I194">
         <v>68.72</v>
@@ -10669,10 +10669,10 @@
     </row>
     <row r="195" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B195" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C195">
         <v>2.04</v>
@@ -10690,7 +10690,7 @@
         <v>0.21999999999999886</v>
       </c>
       <c r="H195" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I195">
         <v>70.040000000000006</v>
@@ -10719,10 +10719,10 @@
     </row>
     <row r="196" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B196" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C196">
         <v>2</v>
@@ -10740,7 +10740,7 @@
         <v>0.52000000000000313</v>
       </c>
       <c r="H196" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I196">
         <v>68.61</v>
@@ -10769,10 +10769,10 @@
     </row>
     <row r="197" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B197" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C197">
         <v>2</v>
@@ -10790,7 +10790,7 @@
         <v>0.60999999999999943</v>
       </c>
       <c r="H197" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I197">
         <v>69.69</v>
@@ -10819,10 +10819,10 @@
     </row>
     <row r="198" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B198" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C198">
         <v>2.02</v>
@@ -10840,7 +10840,7 @@
         <v>0.28999999999999915</v>
       </c>
       <c r="H198" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I198">
         <v>70.069999999999993</v>
@@ -10869,10 +10869,10 @@
     </row>
     <row r="199" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B199" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C199">
         <v>2.04</v>
@@ -10890,7 +10890,7 @@
         <v>0.67000000000000171</v>
       </c>
       <c r="H199" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I199">
         <v>70.069999999999993</v>
@@ -10919,10 +10919,10 @@
     </row>
     <row r="200" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B200" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C200">
         <v>2.0099999999999998</v>
@@ -10940,7 +10940,7 @@
         <v>0.62999999999999545</v>
       </c>
       <c r="H200" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I200">
         <v>73.900000000000006</v>
@@ -10969,10 +10969,10 @@
     </row>
     <row r="201" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B201" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C201">
         <v>1.99</v>
@@ -10990,7 +10990,7 @@
         <v>0.68999999999999773</v>
       </c>
       <c r="H201" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I201">
         <v>71.209999999999994</v>
@@ -11019,10 +11019,10 @@
     </row>
     <row r="202" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B202" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C202">
         <v>1.98</v>
@@ -11040,7 +11040,7 @@
         <v>0.26999999999999602</v>
       </c>
       <c r="H202" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I202">
         <v>70.34</v>
@@ -11069,10 +11069,10 @@
     </row>
     <row r="203" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B203" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C203">
         <v>2.02</v>
@@ -11090,7 +11090,7 @@
         <v>0.79999999999999716</v>
       </c>
       <c r="H203" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I203">
         <v>68.37</v>
@@ -11119,10 +11119,10 @@
     </row>
     <row r="204" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B204" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C204">
         <v>2.04</v>
@@ -11140,7 +11140,7 @@
         <v>0.40999999999999659</v>
       </c>
       <c r="H204" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I204">
         <v>69.569999999999993</v>
@@ -11169,10 +11169,10 @@
     </row>
     <row r="205" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B205" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C205">
         <v>2.04</v>
@@ -11190,7 +11190,7 @@
         <v>0.40000000000000568</v>
       </c>
       <c r="H205" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I205">
         <v>70.290000000000006</v>
@@ -11219,10 +11219,10 @@
     </row>
     <row r="206" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B206" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C206">
         <v>2.0099999999999998</v>
@@ -11240,7 +11240,7 @@
         <v>0.59000000000000341</v>
       </c>
       <c r="H206" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I206">
         <v>67.95</v>
@@ -11269,10 +11269,10 @@
     </row>
     <row r="207" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B207" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C207">
         <v>2.02</v>
@@ -11290,7 +11290,7 @@
         <v>0.29000000000000625</v>
       </c>
       <c r="H207" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I207">
         <v>69.849999999999994</v>
@@ -11319,10 +11319,10 @@
     </row>
     <row r="208" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B208" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C208">
         <v>2.0299999999999998</v>
@@ -11340,7 +11340,7 @@
         <v>0.69999999999998863</v>
       </c>
       <c r="H208" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I208">
         <v>69.819999999999993</v>
@@ -11369,10 +11369,10 @@
     </row>
     <row r="209" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B209" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C209">
         <v>2.0299999999999998</v>
@@ -11390,7 +11390,7 @@
         <v>0.37000000000000455</v>
       </c>
       <c r="H209" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I209">
         <v>70.58</v>
@@ -11419,10 +11419,10 @@
     </row>
     <row r="210" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B210" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C210">
         <v>2.0099999999999998</v>
@@ -11440,7 +11440,7 @@
         <v>0.34999999999999432</v>
       </c>
       <c r="H210" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I210">
         <v>68.94</v>
@@ -11469,10 +11469,10 @@
     </row>
     <row r="211" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B211" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C211">
         <v>2.04</v>
@@ -11490,7 +11490,7 @@
         <v>0.51000000000000512</v>
       </c>
       <c r="H211" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I211">
         <v>69.900000000000006</v>
@@ -11519,10 +11519,10 @@
     </row>
     <row r="212" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B212" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C212">
         <v>2.0099999999999998</v>
@@ -11540,7 +11540,7 @@
         <v>0.98000000000000398</v>
       </c>
       <c r="H212" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I212">
         <v>71.03</v>
@@ -11569,10 +11569,10 @@
     </row>
     <row r="213" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B213" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C213">
         <v>1.97</v>
@@ -11590,7 +11590,7 @@
         <v>1.8100000000000023</v>
       </c>
       <c r="H213" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I213">
         <v>70.98</v>
@@ -11619,10 +11619,10 @@
     </row>
     <row r="214" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B214" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C214">
         <v>2.04</v>
@@ -11640,7 +11640,7 @@
         <v>0.73000000000000398</v>
       </c>
       <c r="H214" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I214">
         <v>71.31</v>
@@ -11669,10 +11669,10 @@
     </row>
     <row r="215" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B215" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C215">
         <v>2.02</v>
@@ -11690,7 +11690,7 @@
         <v>0.28999999999999204</v>
       </c>
       <c r="H215" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I215">
         <v>70.709999999999994</v>
@@ -11719,10 +11719,10 @@
     </row>
     <row r="216" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B216" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C216">
         <v>2.02</v>
@@ -11740,7 +11740,7 @@
         <v>-1.0600000000000023</v>
       </c>
       <c r="H216" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I216">
         <v>68.64</v>
@@ -11769,10 +11769,10 @@
     </row>
     <row r="217" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B217" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C217">
         <v>2.04</v>
@@ -11790,7 +11790,7 @@
         <v>0.34999999999999432</v>
       </c>
       <c r="H217" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I217">
         <v>69.08</v>
@@ -11819,10 +11819,10 @@
     </row>
     <row r="218" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B218" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C218">
         <v>2.02</v>
@@ -11840,7 +11840,7 @@
         <v>0.26999999999999602</v>
       </c>
       <c r="H218" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I218">
         <v>70.12</v>
@@ -11869,10 +11869,10 @@
     </row>
     <row r="219" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B219" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C219">
         <v>2</v>
@@ -11890,7 +11890,7 @@
         <v>0.50999999999999091</v>
       </c>
       <c r="H219" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I219">
         <v>69.72</v>
@@ -11919,10 +11919,10 @@
     </row>
     <row r="220" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B220" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C220">
         <v>2</v>
@@ -11940,7 +11940,7 @@
         <v>0.31000000000000227</v>
       </c>
       <c r="H220" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I220">
         <v>71.599999999999994</v>
@@ -11969,10 +11969,10 @@
     </row>
     <row r="221" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B221" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C221">
         <v>1.98</v>
@@ -11990,7 +11990,7 @@
         <v>0.46999999999999886</v>
       </c>
       <c r="H221" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I221">
         <v>69.11</v>
@@ -12019,10 +12019,10 @@
     </row>
     <row r="222" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B222" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C222">
         <v>2.0099999999999998</v>
@@ -12040,7 +12040,7 @@
         <v>0.17999999999999261</v>
       </c>
       <c r="H222" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I222">
         <v>70.56</v>
@@ -12069,10 +12069,10 @@
     </row>
     <row r="223" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B223" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C223">
         <v>2.04</v>
@@ -12090,7 +12090,7 @@
         <v>0.82999999999999829</v>
       </c>
       <c r="H223" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I223">
         <v>70.900000000000006</v>
@@ -12119,10 +12119,10 @@
     </row>
     <row r="224" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B224" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C224">
         <v>2</v>
@@ -12140,7 +12140,7 @@
         <v>0.55000000000001137</v>
       </c>
       <c r="H224" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I224">
         <v>69.510000000000005</v>
@@ -12169,10 +12169,10 @@
     </row>
     <row r="225" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B225" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C225">
         <v>2</v>
@@ -12190,7 +12190,7 @@
         <v>0.25</v>
       </c>
       <c r="H225" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I225">
         <v>69.8</v>
@@ -12219,10 +12219,10 @@
     </row>
     <row r="226" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B226" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C226">
         <v>2.04</v>
@@ -12240,7 +12240,7 @@
         <v>0.43999999999999773</v>
       </c>
       <c r="H226" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I226">
         <v>70.739999999999995</v>
@@ -12269,10 +12269,10 @@
     </row>
     <row r="227" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B227" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C227">
         <v>2.0499999999999998</v>
@@ -12290,7 +12290,7 @@
         <v>0.36000000000001364</v>
       </c>
       <c r="H227" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I227">
         <v>70.06</v>
@@ -12319,10 +12319,10 @@
     </row>
     <row r="228" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B228" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C228">
         <v>2.02</v>
@@ -12340,7 +12340,7 @@
         <v>0.56000000000000227</v>
       </c>
       <c r="H228" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I228">
         <v>72.05</v>
@@ -12369,10 +12369,10 @@
     </row>
     <row r="229" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B229" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C229">
         <v>1.99</v>
@@ -12390,7 +12390,7 @@
         <v>0.46000000000000796</v>
       </c>
       <c r="H229" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I229">
         <v>69.650000000000006</v>
@@ -12419,10 +12419,10 @@
     </row>
     <row r="230" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B230" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C230">
         <v>2.0299999999999998</v>
@@ -12440,7 +12440,7 @@
         <v>0.46000000000000796</v>
       </c>
       <c r="H230" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I230">
         <v>67.91</v>
@@ -12469,10 +12469,10 @@
     </row>
     <row r="231" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B231" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C231">
         <v>2</v>
@@ -12490,7 +12490,7 @@
         <v>0.57000000000000739</v>
       </c>
       <c r="H231" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I231">
         <v>71.38</v>
@@ -12519,10 +12519,10 @@
     </row>
     <row r="232" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B232" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C232">
         <v>1.96</v>
@@ -12540,7 +12540,7 @@
         <v>0.60999999999999943</v>
       </c>
       <c r="H232" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I232">
         <v>69.73</v>
@@ -12569,10 +12569,10 @@
     </row>
     <row r="233" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B233" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C233">
         <v>2</v>
@@ -12590,7 +12590,7 @@
         <v>0.48000000000000398</v>
       </c>
       <c r="H233" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I233">
         <v>71.459999999999994</v>
@@ -12619,10 +12619,10 @@
     </row>
     <row r="234" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B234" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C234">
         <v>2.0499999999999998</v>
@@ -12640,7 +12640,7 @@
         <v>0.21999999999999886</v>
       </c>
       <c r="H234" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I234">
         <v>70.47</v>
@@ -12669,10 +12669,10 @@
     </row>
     <row r="235" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B235" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C235">
         <v>1.97</v>
@@ -12690,7 +12690,7 @@
         <v>0.31000000000000227</v>
       </c>
       <c r="H235" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I235">
         <v>69.3</v>
@@ -12719,10 +12719,10 @@
     </row>
     <row r="236" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B236" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C236">
         <v>2.02</v>
@@ -12740,7 +12740,7 @@
         <v>0.32999999999999829</v>
       </c>
       <c r="H236" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I236">
         <v>70.010000000000005</v>
@@ -12769,10 +12769,10 @@
     </row>
     <row r="237" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B237" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C237">
         <v>1.95</v>
@@ -12790,7 +12790,7 @@
         <v>0.76000000000000512</v>
       </c>
       <c r="H237" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I237">
         <v>69.06</v>
@@ -12819,10 +12819,10 @@
     </row>
     <row r="238" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B238" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C238">
         <v>2.0299999999999998</v>
@@ -12840,7 +12840,7 @@
         <v>0.80000000000001137</v>
       </c>
       <c r="H238" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I238">
         <v>68.47</v>
@@ -12869,10 +12869,10 @@
     </row>
     <row r="239" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B239" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C239">
         <v>2.04</v>
@@ -12890,7 +12890,7 @@
         <v>0.34999999999999432</v>
       </c>
       <c r="H239" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I239">
         <v>69.739999999999995</v>
@@ -12919,10 +12919,10 @@
     </row>
     <row r="240" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B240" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C240">
         <v>2.0299999999999998</v>
@@ -12940,7 +12940,7 @@
         <v>9.9999999999994316E-2</v>
       </c>
       <c r="H240" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I240">
         <v>70.84</v>
@@ -12969,10 +12969,10 @@
     </row>
     <row r="241" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B241" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C241">
         <v>1.97</v>
@@ -12990,7 +12990,7 @@
         <v>0.23000000000000398</v>
       </c>
       <c r="H241" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I241">
         <v>70.459999999999994</v>

--- a/Data Analysis/1_Data/Aggregates/WSA_Winter_all.xlsx
+++ b/Data Analysis/1_Data/Aggregates/WSA_Winter_all.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mm68tulo\Desktop\Jena Chapter\Data Analysis\1_Data\Aggregates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A489E3D0-1AE0-4674-9B43-A24CCF65D8F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE28F9ED-F5A3-4889-85E9-A6003023411E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -66,9 +66,6 @@
     <t>m Na2PO3 "stable" (g)</t>
   </si>
   <si>
-    <t>WSA (%)</t>
-  </si>
-  <si>
     <t>m sand + org. rest</t>
   </si>
   <si>
@@ -619,6 +616,9 @@
   </si>
   <si>
     <t>agg_overall</t>
+  </si>
+  <si>
+    <t>WSA</t>
   </si>
 </sst>
 </file>
@@ -948,7 +948,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -978,33 +978,33 @@
         <v>9</v>
       </c>
       <c r="L1" t="s">
+        <v>194</v>
+      </c>
+      <c r="M1" t="s">
         <v>10</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
+        <v>193</v>
+      </c>
+      <c r="O1" t="s">
         <v>11</v>
       </c>
-      <c r="N1" t="s">
-        <v>194</v>
-      </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>12</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" t="s">
         <v>14</v>
-      </c>
-      <c r="R1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s">
         <v>16</v>
-      </c>
-      <c r="B2" t="s">
-        <v>17</v>
       </c>
       <c r="C2">
         <v>2</v>
@@ -1022,7 +1022,7 @@
         <v>0.48000000000000398</v>
       </c>
       <c r="H2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I2">
         <v>68.790000000000006</v>
@@ -1054,10 +1054,10 @@
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" t="s">
         <v>19</v>
-      </c>
-      <c r="B3" t="s">
-        <v>20</v>
       </c>
       <c r="C3">
         <v>2.02</v>
@@ -1075,7 +1075,7 @@
         <v>0.48000000000000398</v>
       </c>
       <c r="H3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I3">
         <v>69.790000000000006</v>
@@ -1104,10 +1104,10 @@
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
         <v>22</v>
-      </c>
-      <c r="B4" t="s">
-        <v>23</v>
       </c>
       <c r="C4">
         <v>2.0099999999999998</v>
@@ -1125,7 +1125,7 @@
         <v>0.82999999999999829</v>
       </c>
       <c r="H4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I4">
         <v>67.58</v>
@@ -1154,10 +1154,10 @@
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" t="s">
         <v>25</v>
-      </c>
-      <c r="B5" t="s">
-        <v>26</v>
       </c>
       <c r="C5">
         <v>2</v>
@@ -1175,7 +1175,7 @@
         <v>0.70000000000000284</v>
       </c>
       <c r="H5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I5">
         <v>68.040000000000006</v>
@@ -1204,10 +1204,10 @@
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" t="s">
         <v>28</v>
-      </c>
-      <c r="B6" t="s">
-        <v>29</v>
       </c>
       <c r="C6">
         <v>2.0099999999999998</v>
@@ -1225,7 +1225,7 @@
         <v>0.96999999999999886</v>
       </c>
       <c r="H6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I6">
         <v>67.94</v>
@@ -1254,10 +1254,10 @@
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" t="s">
         <v>31</v>
-      </c>
-      <c r="B7" t="s">
-        <v>32</v>
       </c>
       <c r="C7">
         <v>2.0299999999999998</v>
@@ -1275,7 +1275,7 @@
         <v>0.46999999999999886</v>
       </c>
       <c r="H7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I7">
         <v>70.84</v>
@@ -1304,10 +1304,10 @@
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" t="s">
         <v>34</v>
-      </c>
-      <c r="B8" t="s">
-        <v>35</v>
       </c>
       <c r="C8">
         <v>2</v>
@@ -1325,7 +1325,7 @@
         <v>0.53000000000000114</v>
       </c>
       <c r="H8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I8">
         <v>69.349999999999994</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" t="s">
         <v>37</v>
-      </c>
-      <c r="B9" t="s">
-        <v>38</v>
       </c>
       <c r="C9">
         <v>2</v>
@@ -1375,7 +1375,7 @@
         <v>0.82999999999999829</v>
       </c>
       <c r="H9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I9">
         <v>69.13</v>
@@ -1404,10 +1404,10 @@
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C10">
         <v>2.02</v>
@@ -1425,7 +1425,7 @@
         <v>0.35000000000000853</v>
       </c>
       <c r="H10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I10">
         <v>69.72</v>
@@ -1454,10 +1454,10 @@
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C11">
         <v>2.0499999999999998</v>
@@ -1475,7 +1475,7 @@
         <v>0.51000000000000512</v>
       </c>
       <c r="H11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I11">
         <v>70.47</v>
@@ -1504,10 +1504,10 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C12">
         <v>2.0499999999999998</v>
@@ -1525,7 +1525,7 @@
         <v>0.5</v>
       </c>
       <c r="H12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I12">
         <v>69.069999999999993</v>
@@ -1554,10 +1554,10 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C13">
         <v>1.97</v>
@@ -1575,7 +1575,7 @@
         <v>0.68999999999999773</v>
       </c>
       <c r="H13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I13">
         <v>68.38</v>
@@ -1604,10 +1604,10 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C14">
         <v>1.99</v>
@@ -1625,7 +1625,7 @@
         <v>0.48000000000000398</v>
       </c>
       <c r="H14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I14">
         <v>69.75</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B15" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C15">
         <v>2.0099999999999998</v>
@@ -1675,7 +1675,7 @@
         <v>0.63000000000000966</v>
       </c>
       <c r="H15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I15">
         <v>69.7</v>
@@ -1704,10 +1704,10 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B16" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C16">
         <v>2.02</v>
@@ -1725,7 +1725,7 @@
         <v>0.54000000000000625</v>
       </c>
       <c r="H16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I16">
         <v>70.02</v>
@@ -1754,10 +1754,10 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B17" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C17">
         <v>2</v>
@@ -1775,7 +1775,7 @@
         <v>0.25999999999999091</v>
       </c>
       <c r="H17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I17">
         <v>68.59</v>
@@ -1804,10 +1804,10 @@
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C18">
         <v>2</v>
@@ -1825,7 +1825,7 @@
         <v>0.40999999999999659</v>
       </c>
       <c r="H18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I18">
         <v>70.86</v>
@@ -1854,10 +1854,10 @@
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C19">
         <v>2.0099999999999998</v>
@@ -1875,7 +1875,7 @@
         <v>0.54999999999999716</v>
       </c>
       <c r="H19" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I19">
         <v>69.099999999999994</v>
@@ -1904,10 +1904,10 @@
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C20">
         <v>2.0099999999999998</v>
@@ -1925,7 +1925,7 @@
         <v>0.18000000000000682</v>
       </c>
       <c r="H20" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I20">
         <v>70.3</v>
@@ -1954,10 +1954,10 @@
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B21" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C21">
         <v>2</v>
@@ -1975,7 +1975,7 @@
         <v>0.65999999999999659</v>
       </c>
       <c r="H21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I21">
         <v>69.010000000000005</v>
@@ -2004,10 +2004,10 @@
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B22" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C22">
         <v>2.04</v>
@@ -2025,7 +2025,7 @@
         <v>0.69000000000001194</v>
       </c>
       <c r="H22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I22">
         <v>71.03</v>
@@ -2054,10 +2054,10 @@
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B23" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C23">
         <v>2.02</v>
@@ -2075,7 +2075,7 @@
         <v>0.40000000000000568</v>
       </c>
       <c r="H23" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I23">
         <v>69.64</v>
@@ -2104,10 +2104,10 @@
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B24" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C24">
         <v>1.97</v>
@@ -2125,7 +2125,7 @@
         <v>0.38000000000000966</v>
       </c>
       <c r="H24" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I24">
         <v>70.010000000000005</v>
@@ -2154,10 +2154,10 @@
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B25" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C25">
         <v>2</v>
@@ -2175,7 +2175,7 @@
         <v>0.34000000000000341</v>
       </c>
       <c r="H25" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I25">
         <v>70.930000000000007</v>
@@ -2204,10 +2204,10 @@
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B26" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C26">
         <v>1.99</v>
@@ -2225,7 +2225,7 @@
         <v>0.34000000000000341</v>
       </c>
       <c r="H26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I26">
         <v>71.11</v>
@@ -2254,10 +2254,10 @@
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C27">
         <v>2</v>
@@ -2275,7 +2275,7 @@
         <v>0.82999999999999829</v>
       </c>
       <c r="H27" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I27">
         <v>71.22</v>
@@ -2304,10 +2304,10 @@
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B28" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C28">
         <v>2.02</v>
@@ -2325,7 +2325,7 @@
         <v>0.29000000000000625</v>
       </c>
       <c r="H28" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I28">
         <v>71.02</v>
@@ -2354,10 +2354,10 @@
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B29" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C29">
         <v>2.0099999999999998</v>
@@ -2375,7 +2375,7 @@
         <v>0.35999999999999943</v>
       </c>
       <c r="H29" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I29">
         <v>69.52</v>
@@ -2404,10 +2404,10 @@
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C30">
         <v>1.99</v>
@@ -2425,7 +2425,7 @@
         <v>0.37000000000000455</v>
       </c>
       <c r="H30" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I30">
         <v>68.209999999999994</v>
@@ -2454,10 +2454,10 @@
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C31">
         <v>2</v>
@@ -2475,7 +2475,7 @@
         <v>0.61999999999999034</v>
       </c>
       <c r="H31" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I31">
         <v>70.2</v>
@@ -2504,10 +2504,10 @@
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C32">
         <v>1.98</v>
@@ -2525,7 +2525,7 @@
         <v>0.53000000000000114</v>
       </c>
       <c r="H32" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I32">
         <v>70.040000000000006</v>
@@ -2554,10 +2554,10 @@
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B33" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C33">
         <v>2</v>
@@ -2575,7 +2575,7 @@
         <v>0.36999999999999034</v>
       </c>
       <c r="H33" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I33">
         <v>71.08</v>
@@ -2604,10 +2604,10 @@
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B34" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C34">
         <v>2.0099999999999998</v>
@@ -2625,7 +2625,7 @@
         <v>0.74000000000000909</v>
       </c>
       <c r="H34" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I34">
         <v>72.930000000000007</v>
@@ -2654,10 +2654,10 @@
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B35" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C35">
         <v>2.0299999999999998</v>
@@ -2675,7 +2675,7 @@
         <v>0.37999999999999545</v>
       </c>
       <c r="H35" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I35">
         <v>70.62</v>
@@ -2704,10 +2704,10 @@
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B36" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C36">
         <v>1.99</v>
@@ -2725,7 +2725,7 @@
         <v>0.20999999999999375</v>
       </c>
       <c r="H36" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I36">
         <v>72.05</v>
@@ -2754,10 +2754,10 @@
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B37" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C37">
         <v>2.0299999999999998</v>
@@ -2775,7 +2775,7 @@
         <v>0.25</v>
       </c>
       <c r="H37" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I37">
         <v>71.13</v>
@@ -2804,10 +2804,10 @@
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B38" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C38">
         <v>2</v>
@@ -2825,7 +2825,7 @@
         <v>0.45999999999999375</v>
       </c>
       <c r="H38" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I38">
         <v>69.97</v>
@@ -2854,10 +2854,10 @@
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B39" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C39">
         <v>2.04</v>
@@ -2875,7 +2875,7 @@
         <v>0.24000000000000909</v>
       </c>
       <c r="H39" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I39">
         <v>68.64</v>
@@ -2904,10 +2904,10 @@
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B40" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C40">
         <v>1.99</v>
@@ -2925,7 +2925,7 @@
         <v>0.35000000000000853</v>
       </c>
       <c r="H40" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I40">
         <v>69.95</v>
@@ -2954,10 +2954,10 @@
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B41" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C41">
         <v>2.0499999999999998</v>
@@ -2975,7 +2975,7 @@
         <v>0.59000000000000341</v>
       </c>
       <c r="H41" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I41">
         <v>104.25</v>
@@ -3004,10 +3004,10 @@
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C42">
         <v>1.98</v>
@@ -3025,7 +3025,7 @@
         <v>0.27000000000001023</v>
       </c>
       <c r="H42" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I42">
         <v>67.569999999999993</v>
@@ -3046,7 +3046,7 @@
         <v>86.174242424243161</v>
       </c>
       <c r="O42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P42">
         <v>0.18375</v>
@@ -3060,10 +3060,10 @@
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B43" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C43">
         <v>2</v>
@@ -3081,7 +3081,7 @@
         <v>0.42000000000000171</v>
       </c>
       <c r="H43" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I43">
         <v>71.3</v>
@@ -3110,10 +3110,10 @@
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B44" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C44">
         <v>1.98</v>
@@ -3131,7 +3131,7 @@
         <v>0.20999999999999375</v>
       </c>
       <c r="H44" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I44">
         <v>68.709999999999994</v>
@@ -3160,10 +3160,10 @@
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B45" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C45">
         <v>2</v>
@@ -3181,7 +3181,7 @@
         <v>0.56999999999999318</v>
       </c>
       <c r="H45" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I45">
         <v>70.86</v>
@@ -3210,10 +3210,10 @@
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B46" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C46">
         <v>2.02</v>
@@ -3231,7 +3231,7 @@
         <v>0.32999999999999829</v>
       </c>
       <c r="H46" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I46">
         <v>68.91</v>
@@ -3260,10 +3260,10 @@
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B47" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C47">
         <v>2.04</v>
@@ -3281,7 +3281,7 @@
         <v>1.0700000000000074</v>
       </c>
       <c r="H47" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I47">
         <v>70.47</v>
@@ -3310,10 +3310,10 @@
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B48" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C48">
         <v>2.04</v>
@@ -3331,7 +3331,7 @@
         <v>0.35000000000000853</v>
       </c>
       <c r="H48" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I48">
         <v>70.489999999999995</v>
@@ -3360,10 +3360,10 @@
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B49" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C49">
         <v>2</v>
@@ -3381,7 +3381,7 @@
         <v>0.42999999999999261</v>
       </c>
       <c r="H49" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I49">
         <v>69.180000000000007</v>
@@ -3410,10 +3410,10 @@
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B50" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C50">
         <v>2</v>
@@ -3431,7 +3431,7 @@
         <v>0.71999999999999886</v>
       </c>
       <c r="H50" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I50">
         <v>71.650000000000006</v>
@@ -3460,10 +3460,10 @@
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B51" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C51">
         <v>2</v>
@@ -3481,7 +3481,7 @@
         <v>0.15000000000000568</v>
       </c>
       <c r="H51" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I51">
         <v>69.319999999999993</v>
@@ -3510,10 +3510,10 @@
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B52" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C52">
         <v>2.0099999999999998</v>
@@ -3531,7 +3531,7 @@
         <v>0.45000000000000284</v>
       </c>
       <c r="H52" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I52">
         <v>70.459999999999994</v>
@@ -3560,10 +3560,10 @@
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B53" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C53">
         <v>2.02</v>
@@ -3581,7 +3581,7 @@
         <v>0.14000000000000057</v>
       </c>
       <c r="H53" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I53">
         <v>67.989999999999995</v>
@@ -3610,10 +3610,10 @@
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B54" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C54">
         <v>2</v>
@@ -3631,7 +3631,7 @@
         <v>0.43999999999999773</v>
       </c>
       <c r="H54" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I54">
         <v>69.08</v>
@@ -3660,10 +3660,10 @@
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B55" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C55">
         <v>2.04</v>
@@ -3681,7 +3681,7 @@
         <v>6.9999999999993179E-2</v>
       </c>
       <c r="H55" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I55">
         <v>71.319999999999993</v>
@@ -3710,10 +3710,10 @@
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B56" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C56">
         <v>2.0299999999999998</v>
@@ -3731,7 +3731,7 @@
         <v>0.26999999999999602</v>
       </c>
       <c r="H56" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I56">
         <v>68.61</v>
@@ -3760,10 +3760,10 @@
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B57" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C57">
         <v>1.98</v>
@@ -3781,7 +3781,7 @@
         <v>0.35999999999999943</v>
       </c>
       <c r="H57" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I57">
         <v>69.84</v>
@@ -3810,10 +3810,10 @@
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B58" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C58">
         <v>2.02</v>
@@ -3831,7 +3831,7 @@
         <v>0.32999999999999829</v>
       </c>
       <c r="H58" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I58">
         <v>70.36</v>
@@ -3860,10 +3860,10 @@
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B59" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C59">
         <v>2.04</v>
@@ -3881,7 +3881,7 @@
         <v>0.9100000000000108</v>
       </c>
       <c r="H59" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I59">
         <v>68.040000000000006</v>
@@ -3910,10 +3910,10 @@
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B60" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C60">
         <v>2</v>
@@ -3931,7 +3931,7 @@
         <v>0.50999999999999091</v>
       </c>
       <c r="H60" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I60">
         <v>69.69</v>
@@ -3960,10 +3960,10 @@
     </row>
     <row r="61" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B61" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C61">
         <v>2.0499999999999998</v>
@@ -3981,7 +3981,7 @@
         <v>0.78000000000000114</v>
       </c>
       <c r="H61" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I61">
         <v>71.459999999999994</v>
@@ -4010,10 +4010,10 @@
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B62" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C62">
         <v>2.0099999999999998</v>
@@ -4031,7 +4031,7 @@
         <v>0.46999999999999886</v>
       </c>
       <c r="H62" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I62">
         <v>69.739999999999995</v>
@@ -4060,10 +4060,10 @@
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B63" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C63">
         <v>1.98</v>
@@ -4081,7 +4081,7 @@
         <v>0.28000000000000114</v>
       </c>
       <c r="H63" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I63">
         <v>70.97</v>
@@ -4110,10 +4110,10 @@
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B64" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C64">
         <v>1.98</v>
@@ -4131,7 +4131,7 @@
         <v>0.28000000000000114</v>
       </c>
       <c r="H64" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I64">
         <v>67.91</v>
@@ -4160,10 +4160,10 @@
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B65" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C65">
         <v>1.98</v>
@@ -4181,7 +4181,7 @@
         <v>0.79000000000000625</v>
       </c>
       <c r="H65" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I65">
         <v>70.34</v>
@@ -4210,10 +4210,10 @@
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B66" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C66">
         <v>2.0099999999999998</v>
@@ -4231,7 +4231,7 @@
         <v>0.20999999999999375</v>
       </c>
       <c r="H66" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I66">
         <v>70.02</v>
@@ -4260,10 +4260,10 @@
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B67" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C67">
         <v>2</v>
@@ -4281,7 +4281,7 @@
         <v>0.18999999999999773</v>
       </c>
       <c r="H67" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I67">
         <v>69.64</v>
@@ -4310,10 +4310,10 @@
     </row>
     <row r="68" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B68" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C68">
         <v>2.04</v>
@@ -4331,7 +4331,7 @@
         <v>0.18000000000000682</v>
       </c>
       <c r="H68" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I68">
         <v>70.459999999999994</v>
@@ -4360,10 +4360,10 @@
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B69" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C69">
         <v>2</v>
@@ -4381,7 +4381,7 @@
         <v>0.12000000000000455</v>
       </c>
       <c r="H69" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I69">
         <v>71.38</v>
@@ -4410,10 +4410,10 @@
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B70" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C70">
         <v>1.99</v>
@@ -4431,7 +4431,7 @@
         <v>0.14999999999999147</v>
       </c>
       <c r="H70" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I70">
         <v>69.73</v>
@@ -4460,10 +4460,10 @@
     </row>
     <row r="71" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B71" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C71">
         <v>2.04</v>
@@ -4481,7 +4481,7 @@
         <v>0.34000000000000341</v>
       </c>
       <c r="H71" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I71">
         <v>68.36</v>
@@ -4510,10 +4510,10 @@
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B72" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C72">
         <v>2.04</v>
@@ -4531,7 +4531,7 @@
         <v>0.23000000000000398</v>
       </c>
       <c r="H72" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I72">
         <v>68.59</v>
@@ -4560,10 +4560,10 @@
     </row>
     <row r="73" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B73" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C73">
         <v>2.0099999999999998</v>
@@ -4581,7 +4581,7 @@
         <v>0.43999999999999773</v>
       </c>
       <c r="H73" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I73">
         <v>70.83</v>
@@ -4610,10 +4610,10 @@
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B74" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C74">
         <v>2.0099999999999998</v>
@@ -4631,7 +4631,7 @@
         <v>0.73000000000000398</v>
       </c>
       <c r="H74" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I74">
         <v>71.23</v>
@@ -4660,10 +4660,10 @@
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B75" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C75">
         <v>2.0099999999999998</v>
@@ -4681,7 +4681,7 @@
         <v>0.31000000000000227</v>
       </c>
       <c r="H75" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I75">
         <v>71.459999999999994</v>
@@ -4710,10 +4710,10 @@
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B76" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C76">
         <v>1.97</v>
@@ -4731,7 +4731,7 @@
         <v>0.40999999999999659</v>
       </c>
       <c r="H76" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I76">
         <v>69.13</v>
@@ -4760,10 +4760,10 @@
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B77" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C77">
         <v>1.95</v>
@@ -4781,7 +4781,7 @@
         <v>0.28999999999999204</v>
       </c>
       <c r="H77" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I77">
         <v>70.290000000000006</v>
@@ -4810,10 +4810,10 @@
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B78" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C78">
         <v>2.0299999999999998</v>
@@ -4831,7 +4831,7 @@
         <v>0.59000000000000341</v>
       </c>
       <c r="H78" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I78">
         <v>69.209999999999994</v>
@@ -4860,10 +4860,10 @@
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B79" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C79">
         <v>1.98</v>
@@ -4881,7 +4881,7 @@
         <v>0.58000000000001251</v>
       </c>
       <c r="H79" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I79">
         <v>68.59</v>
@@ -4910,10 +4910,10 @@
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B80" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C80">
         <v>2.02</v>
@@ -4931,7 +4931,7 @@
         <v>0.68000000000000682</v>
       </c>
       <c r="H80" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I80">
         <v>69.62</v>
@@ -4960,10 +4960,10 @@
     </row>
     <row r="81" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B81" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C81">
         <v>1.98</v>
@@ -4981,7 +4981,7 @@
         <v>0.20999999999999375</v>
       </c>
       <c r="H81" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I81">
         <v>69.569999999999993</v>
@@ -5010,10 +5010,10 @@
     </row>
     <row r="82" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B82" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C82">
         <v>1.98</v>
@@ -5031,7 +5031,7 @@
         <v>0.21999999999999886</v>
       </c>
       <c r="H82" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I82">
         <v>67.91</v>
@@ -5063,10 +5063,10 @@
     </row>
     <row r="83" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B83" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C83">
         <v>2</v>
@@ -5084,7 +5084,7 @@
         <v>0.57999999999999829</v>
       </c>
       <c r="H83" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I83">
         <v>67.94</v>
@@ -5113,10 +5113,10 @@
     </row>
     <row r="84" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B84" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C84">
         <v>1.99</v>
@@ -5134,7 +5134,7 @@
         <v>0.32999999999999829</v>
       </c>
       <c r="H84" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I84">
         <v>67.89</v>
@@ -5163,10 +5163,10 @@
     </row>
     <row r="85" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B85" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C85">
         <v>2</v>
@@ -5184,7 +5184,7 @@
         <v>0.75</v>
       </c>
       <c r="H85" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I85">
         <v>69.02</v>
@@ -5213,10 +5213,10 @@
     </row>
     <row r="86" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B86" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C86">
         <v>1.97</v>
@@ -5234,7 +5234,7 @@
         <v>0.22000000000001307</v>
       </c>
       <c r="H86" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I86">
         <v>69.16</v>
@@ -5263,10 +5263,10 @@
     </row>
     <row r="87" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B87" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C87">
         <v>1.98</v>
@@ -5284,7 +5284,7 @@
         <v>0.85000000000000853</v>
       </c>
       <c r="H87" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I87">
         <v>68.78</v>
@@ -5313,10 +5313,10 @@
     </row>
     <row r="88" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B88" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C88">
         <v>2.0499999999999998</v>
@@ -5334,7 +5334,7 @@
         <v>0.34000000000000341</v>
       </c>
       <c r="H88" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I88">
         <v>70.349999999999994</v>
@@ -5363,10 +5363,10 @@
     </row>
     <row r="89" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B89" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C89">
         <v>2.0099999999999998</v>
@@ -5384,7 +5384,7 @@
         <v>0.17999999999999261</v>
       </c>
       <c r="H89" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I89">
         <v>69.84</v>
@@ -5413,10 +5413,10 @@
     </row>
     <row r="90" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B90" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C90">
         <v>2.0299999999999998</v>
@@ -5434,7 +5434,7 @@
         <v>0.15999999999999659</v>
       </c>
       <c r="H90" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I90">
         <v>69.55</v>
@@ -5463,10 +5463,10 @@
     </row>
     <row r="91" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B91" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C91">
         <v>2.04</v>
@@ -5484,7 +5484,7 @@
         <v>0.33000000000001251</v>
       </c>
       <c r="H91" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I91">
         <v>70.58</v>
@@ -5513,10 +5513,10 @@
     </row>
     <row r="92" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B92" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C92">
         <v>2</v>
@@ -5534,7 +5534,7 @@
         <v>0.18000000000000682</v>
       </c>
       <c r="H92" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I92">
         <v>70.98</v>
@@ -5563,10 +5563,10 @@
     </row>
     <row r="93" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B93" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C93">
         <v>2.0499999999999998</v>
@@ -5584,7 +5584,7 @@
         <v>0.21999999999999886</v>
       </c>
       <c r="H93" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I93">
         <v>68.72</v>
@@ -5613,10 +5613,10 @@
     </row>
     <row r="94" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B94" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C94">
         <v>2</v>
@@ -5634,7 +5634,7 @@
         <v>0.28999999999999204</v>
       </c>
       <c r="H94" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I94">
         <v>69.13</v>
@@ -5663,10 +5663,10 @@
     </row>
     <row r="95" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B95" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C95">
         <v>2.04</v>
@@ -5684,7 +5684,7 @@
         <v>0.50999999999999091</v>
       </c>
       <c r="H95" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I95">
         <v>71.3</v>
@@ -5713,10 +5713,10 @@
     </row>
     <row r="96" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B96" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C96">
         <v>2.0299999999999998</v>
@@ -5734,7 +5734,7 @@
         <v>0.5</v>
       </c>
       <c r="H96" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I96">
         <v>69.64</v>
@@ -5763,10 +5763,10 @@
     </row>
     <row r="97" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B97" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C97">
         <v>2.0099999999999998</v>
@@ -5784,7 +5784,7 @@
         <v>4.9999999999997158E-2</v>
       </c>
       <c r="H97" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I97">
         <v>69.72</v>
@@ -5813,10 +5813,10 @@
     </row>
     <row r="98" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B98" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C98">
         <v>1.99</v>
@@ -5834,7 +5834,7 @@
         <v>0.57000000000000739</v>
       </c>
       <c r="H98" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I98">
         <v>68.73</v>
@@ -5863,10 +5863,10 @@
     </row>
     <row r="99" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B99" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C99">
         <v>2.02</v>
@@ -5884,7 +5884,7 @@
         <v>0.29000000000000625</v>
       </c>
       <c r="H99" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I99">
         <v>68.959999999999994</v>
@@ -5913,10 +5913,10 @@
     </row>
     <row r="100" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B100" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C100">
         <v>2.0099999999999998</v>
@@ -5934,7 +5934,7 @@
         <v>0.17000000000000171</v>
       </c>
       <c r="H100" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I100">
         <v>71.03</v>
@@ -5963,10 +5963,10 @@
     </row>
     <row r="101" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B101" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C101">
         <v>2.0099999999999998</v>
@@ -5984,7 +5984,7 @@
         <v>0.42999999999999261</v>
       </c>
       <c r="H101" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I101">
         <v>68.64</v>
@@ -6013,10 +6013,10 @@
     </row>
     <row r="102" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B102" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C102">
         <v>2</v>
@@ -6034,7 +6034,7 @@
         <v>0.51000000000000512</v>
       </c>
       <c r="H102" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I102">
         <v>69.900000000000006</v>
@@ -6063,10 +6063,10 @@
     </row>
     <row r="103" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B103" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C103">
         <v>2.0499999999999998</v>
@@ -6084,7 +6084,7 @@
         <v>0.50999999999999091</v>
       </c>
       <c r="H103" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I103">
         <v>69.17</v>
@@ -6113,10 +6113,10 @@
     </row>
     <row r="104" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B104" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C104">
         <v>2</v>
@@ -6134,7 +6134,7 @@
         <v>9.9999999999994316E-2</v>
       </c>
       <c r="H104" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I104">
         <v>70.709999999999994</v>
@@ -6163,10 +6163,10 @@
     </row>
     <row r="105" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B105" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C105">
         <v>1.99</v>
@@ -6184,7 +6184,7 @@
         <v>0.53000000000000114</v>
       </c>
       <c r="H105" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I105">
         <v>67.989999999999995</v>
@@ -6213,10 +6213,10 @@
     </row>
     <row r="106" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B106" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C106">
         <v>2</v>
@@ -6234,7 +6234,7 @@
         <v>0.10000000000000853</v>
       </c>
       <c r="H106" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I106">
         <v>69.95</v>
@@ -6263,10 +6263,10 @@
     </row>
     <row r="107" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B107" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C107">
         <v>1.98</v>
@@ -6284,7 +6284,7 @@
         <v>0.79999999999999716</v>
       </c>
       <c r="H107" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I107">
         <v>68.08</v>
@@ -6313,10 +6313,10 @@
     </row>
     <row r="108" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B108" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C108">
         <v>2.0299999999999998</v>
@@ -6334,7 +6334,7 @@
         <v>0.19000000000001194</v>
       </c>
       <c r="H108" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I108">
         <v>68.58</v>
@@ -6363,10 +6363,10 @@
     </row>
     <row r="109" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B109" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C109">
         <v>1.97</v>
@@ -6384,7 +6384,7 @@
         <v>0.72999999999998977</v>
       </c>
       <c r="H109" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I109">
         <v>71.28</v>
@@ -6413,10 +6413,10 @@
     </row>
     <row r="110" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B110" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C110">
         <v>1.99</v>
@@ -6434,7 +6434,7 @@
         <v>0.34000000000000341</v>
       </c>
       <c r="H110" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I110">
         <v>69.760000000000005</v>
@@ -6463,10 +6463,10 @@
     </row>
     <row r="111" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B111" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C111">
         <v>1.98</v>
@@ -6484,7 +6484,7 @@
         <v>0.82000000000000739</v>
       </c>
       <c r="H111" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I111">
         <v>70.849999999999994</v>
@@ -6513,10 +6513,10 @@
     </row>
     <row r="112" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B112" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C112">
         <v>1.99</v>
@@ -6534,7 +6534,7 @@
         <v>0.57999999999999829</v>
       </c>
       <c r="H112" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I112">
         <v>71.08</v>
@@ -6563,10 +6563,10 @@
     </row>
     <row r="113" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B113" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C113">
         <v>2</v>
@@ -6584,7 +6584,7 @@
         <v>0.73000000000000398</v>
       </c>
       <c r="H113" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I113">
         <v>68.56</v>
@@ -6613,10 +6613,10 @@
     </row>
     <row r="114" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B114" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C114">
         <v>2</v>
@@ -6634,7 +6634,7 @@
         <v>0.5899999999999892</v>
       </c>
       <c r="H114" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I114">
         <v>70.19</v>
@@ -6663,10 +6663,10 @@
     </row>
     <row r="115" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B115" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C115">
         <v>2.02</v>
@@ -6684,7 +6684,7 @@
         <v>0.40000000000000568</v>
       </c>
       <c r="H115" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I115">
         <v>69.38</v>
@@ -6713,10 +6713,10 @@
     </row>
     <row r="116" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B116" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C116">
         <v>2.02</v>
@@ -6734,7 +6734,7 @@
         <v>0.67000000000000171</v>
       </c>
       <c r="H116" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I116">
         <v>69.58</v>
@@ -6763,10 +6763,10 @@
     </row>
     <row r="117" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B117" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C117">
         <v>2.04</v>
@@ -6784,7 +6784,7 @@
         <v>0.29000000000000625</v>
       </c>
       <c r="H117" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I117">
         <v>70.16</v>
@@ -6813,10 +6813,10 @@
     </row>
     <row r="118" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B118" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C118">
         <v>2.02</v>
@@ -6834,7 +6834,7 @@
         <v>0.32000000000000739</v>
       </c>
       <c r="H118" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I118">
         <v>70.459999999999994</v>
@@ -6863,10 +6863,10 @@
     </row>
     <row r="119" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B119" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C119">
         <v>2.0099999999999998</v>
@@ -6884,7 +6884,7 @@
         <v>0.26999999999999602</v>
       </c>
       <c r="H119" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I119">
         <v>69.25</v>
@@ -6913,10 +6913,10 @@
     </row>
     <row r="120" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B120" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C120">
         <v>2.04</v>
@@ -6934,7 +6934,7 @@
         <v>0.68999999999999773</v>
       </c>
       <c r="H120" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I120">
         <v>70.099999999999994</v>
@@ -6963,10 +6963,10 @@
     </row>
     <row r="121" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B121" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C121">
         <v>2.0299999999999998</v>
@@ -6984,7 +6984,7 @@
         <v>0.73999999999999488</v>
       </c>
       <c r="H121" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I121">
         <v>71.06</v>
@@ -7013,10 +7013,10 @@
     </row>
     <row r="122" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B122" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C122">
         <v>2.0099999999999998</v>
@@ -7034,7 +7034,7 @@
         <v>0.35000000000000142</v>
       </c>
       <c r="H122" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I122">
         <v>70.31</v>
@@ -7066,10 +7066,10 @@
     </row>
     <row r="123" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B123" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C123">
         <v>2.0099999999999998</v>
@@ -7087,7 +7087,7 @@
         <v>0.64999999999999858</v>
       </c>
       <c r="H123" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I123">
         <v>70.2</v>
@@ -7116,10 +7116,10 @@
     </row>
     <row r="124" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B124" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C124">
         <v>2.02</v>
@@ -7137,7 +7137,7 @@
         <v>0.34999999999999432</v>
       </c>
       <c r="H124" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I124">
         <v>69.39</v>
@@ -7166,10 +7166,10 @@
     </row>
     <row r="125" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B125" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C125">
         <v>2</v>
@@ -7187,7 +7187,7 @@
         <v>0.20000000000000284</v>
       </c>
       <c r="H125" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I125">
         <v>71.069999999999993</v>
@@ -7216,10 +7216,10 @@
     </row>
     <row r="126" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B126" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C126">
         <v>2</v>
@@ -7237,7 +7237,7 @@
         <v>0.51000000000000512</v>
       </c>
       <c r="H126" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I126">
         <v>70.23</v>
@@ -7266,10 +7266,10 @@
     </row>
     <row r="127" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B127" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C127">
         <v>1.97</v>
@@ -7287,7 +7287,7 @@
         <v>0.42999999999999972</v>
       </c>
       <c r="H127" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I127">
         <v>69.62</v>
@@ -7316,10 +7316,10 @@
     </row>
     <row r="128" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B128" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C128">
         <v>2.0299999999999998</v>
@@ -7337,7 +7337,7 @@
         <v>0.38000000000000256</v>
       </c>
       <c r="H128" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I128">
         <v>73.260000000000005</v>
@@ -7366,10 +7366,10 @@
     </row>
     <row r="129" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B129" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C129">
         <v>2.02</v>
@@ -7387,7 +7387,7 @@
         <v>0.74000000000000199</v>
       </c>
       <c r="H129" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I129">
         <v>68.55</v>
@@ -7416,10 +7416,10 @@
     </row>
     <row r="130" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B130" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C130">
         <v>2</v>
@@ -7437,7 +7437,7 @@
         <v>0.35000000000000142</v>
       </c>
       <c r="H130" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I130">
         <v>69.78</v>
@@ -7466,10 +7466,10 @@
     </row>
     <row r="131" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B131" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C131">
         <v>1.96</v>
@@ -7487,7 +7487,7 @@
         <v>1.009999999999998</v>
       </c>
       <c r="H131" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I131">
         <v>71.86</v>
@@ -7516,10 +7516,10 @@
     </row>
     <row r="132" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B132" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C132">
         <v>1.99</v>
@@ -7537,7 +7537,7 @@
         <v>0.24000000000000199</v>
       </c>
       <c r="H132" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I132">
         <v>70.23</v>
@@ -7566,10 +7566,10 @@
     </row>
     <row r="133" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B133" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C133">
         <v>2.02</v>
@@ -7587,7 +7587,7 @@
         <v>0.40999999999999659</v>
       </c>
       <c r="H133" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I133">
         <v>68.099999999999994</v>
@@ -7616,10 +7616,10 @@
     </row>
     <row r="134" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B134" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C134">
         <v>2.04</v>
@@ -7637,7 +7637,7 @@
         <v>0.31000000000000227</v>
       </c>
       <c r="H134" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I134">
         <v>69.349999999999994</v>
@@ -7666,10 +7666,10 @@
     </row>
     <row r="135" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B135" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C135">
         <v>2.0099999999999998</v>
@@ -7687,7 +7687,7 @@
         <v>0.36999999999999744</v>
       </c>
       <c r="H135" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I135">
         <v>69.05</v>
@@ -7716,10 +7716,10 @@
     </row>
     <row r="136" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B136" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C136">
         <v>2.0099999999999998</v>
@@ -7737,7 +7737,7 @@
         <v>0.14000000000000057</v>
       </c>
       <c r="H136" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I136">
         <v>69.7</v>
@@ -7766,10 +7766,10 @@
     </row>
     <row r="137" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B137" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C137">
         <v>2.0299999999999998</v>
@@ -7787,7 +7787,7 @@
         <v>0.39000000000000057</v>
       </c>
       <c r="H137" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I137">
         <v>70.040000000000006</v>
@@ -7816,10 +7816,10 @@
     </row>
     <row r="138" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B138" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C138">
         <v>1.98</v>
@@ -7837,7 +7837,7 @@
         <v>0.68999999999999773</v>
       </c>
       <c r="H138" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I138">
         <v>68.069999999999993</v>
@@ -7866,10 +7866,10 @@
     </row>
     <row r="139" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B139" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C139">
         <v>1.96</v>
@@ -7887,7 +7887,7 @@
         <v>0.36999999999999744</v>
       </c>
       <c r="H139" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I139">
         <v>69.66</v>
@@ -7916,10 +7916,10 @@
     </row>
     <row r="140" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B140" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C140">
         <v>1.98</v>
@@ -7937,7 +7937,7 @@
         <v>0.32000000000000028</v>
       </c>
       <c r="H140" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I140">
         <v>70.06</v>
@@ -7966,10 +7966,10 @@
     </row>
     <row r="141" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B141" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C141">
         <v>2</v>
@@ -7987,7 +7987,7 @@
         <v>0.64000000000000057</v>
       </c>
       <c r="H141" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I141">
         <v>69.83</v>
@@ -8016,10 +8016,10 @@
     </row>
     <row r="142" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B142" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C142">
         <v>2.04</v>
@@ -8037,7 +8037,7 @@
         <v>0.54999999999999716</v>
       </c>
       <c r="H142" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I142">
         <v>70.739999999999995</v>
@@ -8066,10 +8066,10 @@
     </row>
     <row r="143" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B143" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C143">
         <v>2.0299999999999998</v>
@@ -8087,7 +8087,7 @@
         <v>0.74000000000000199</v>
       </c>
       <c r="H143" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I143">
         <v>69.11</v>
@@ -8116,10 +8116,10 @@
     </row>
     <row r="144" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B144" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C144">
         <v>1.95</v>
@@ -8137,7 +8137,7 @@
         <v>0.31000000000000227</v>
       </c>
       <c r="H144" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I144">
         <v>71.12</v>
@@ -8166,10 +8166,10 @@
     </row>
     <row r="145" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B145" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C145">
         <v>2.0499999999999998</v>
@@ -8187,7 +8187,7 @@
         <v>0.50999999999999801</v>
       </c>
       <c r="H145" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I145">
         <v>68.680000000000007</v>
@@ -8216,10 +8216,10 @@
     </row>
     <row r="146" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B146" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C146">
         <v>2.04</v>
@@ -8237,7 +8237,7 @@
         <v>0.82999999999999829</v>
       </c>
       <c r="H146" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I146">
         <v>68.5</v>
@@ -8266,10 +8266,10 @@
     </row>
     <row r="147" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B147" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C147">
         <v>2</v>
@@ -8287,7 +8287,7 @@
         <v>0.56000000000000227</v>
       </c>
       <c r="H147" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I147">
         <v>70.78</v>
@@ -8316,10 +8316,10 @@
     </row>
     <row r="148" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B148" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C148">
         <v>1.99</v>
@@ -8337,7 +8337,7 @@
         <v>0.28999999999999915</v>
       </c>
       <c r="H148" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I148">
         <v>68.7</v>
@@ -8366,10 +8366,10 @@
     </row>
     <row r="149" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B149" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C149">
         <v>2.04</v>
@@ -8387,7 +8387,7 @@
         <v>0.63999999999999346</v>
       </c>
       <c r="H149" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I149">
         <v>69.069999999999993</v>
@@ -8416,10 +8416,10 @@
     </row>
     <row r="150" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B150" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C150">
         <v>2.0299999999999998</v>
@@ -8437,7 +8437,7 @@
         <v>0.67999999999999972</v>
       </c>
       <c r="H150" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I150">
         <v>70.66</v>
@@ -8466,10 +8466,10 @@
     </row>
     <row r="151" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B151" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C151">
         <v>1.95</v>
@@ -8487,7 +8487,7 @@
         <v>0.81000000000000227</v>
       </c>
       <c r="H151" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I151">
         <v>69.19</v>
@@ -8516,10 +8516,10 @@
     </row>
     <row r="152" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B152" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C152">
         <v>2.02</v>
@@ -8537,7 +8537,7 @@
         <v>0.25</v>
       </c>
       <c r="H152" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I152">
         <v>68.61</v>
@@ -8566,10 +8566,10 @@
     </row>
     <row r="153" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B153" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C153">
         <v>1.97</v>
@@ -8587,7 +8587,7 @@
         <v>0.38999999999999346</v>
       </c>
       <c r="H153" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I153">
         <v>68.489999999999995</v>
@@ -8616,10 +8616,10 @@
     </row>
     <row r="154" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B154" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C154">
         <v>2</v>
@@ -8637,7 +8637,7 @@
         <v>9.9999999999994316E-2</v>
       </c>
       <c r="H154" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I154">
         <v>71.03</v>
@@ -8666,10 +8666,10 @@
     </row>
     <row r="155" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B155" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C155">
         <v>2</v>
@@ -8687,7 +8687,7 @@
         <v>0.52000000000000313</v>
       </c>
       <c r="H155" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I155">
         <v>69.12</v>
@@ -8716,10 +8716,10 @@
     </row>
     <row r="156" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B156" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C156">
         <v>1.96</v>
@@ -8737,7 +8737,7 @@
         <v>0.42000000000000171</v>
       </c>
       <c r="H156" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I156">
         <v>70.66</v>
@@ -8766,10 +8766,10 @@
     </row>
     <row r="157" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B157" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C157">
         <v>1.99</v>
@@ -8787,7 +8787,7 @@
         <v>0.36999999999999744</v>
       </c>
       <c r="H157" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I157">
         <v>68.599999999999994</v>
@@ -8816,10 +8816,10 @@
     </row>
     <row r="158" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B158" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C158">
         <v>1.95</v>
@@ -8837,7 +8837,7 @@
         <v>0.46000000000000085</v>
       </c>
       <c r="H158" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I158">
         <v>69.89</v>
@@ -8866,10 +8866,10 @@
     </row>
     <row r="159" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B159" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C159">
         <v>2.0499999999999998</v>
@@ -8887,7 +8887,7 @@
         <v>0.50999999999999801</v>
       </c>
       <c r="H159" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I159">
         <v>70.56</v>
@@ -8916,10 +8916,10 @@
     </row>
     <row r="160" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B160" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C160">
         <v>2</v>
@@ -8937,7 +8937,7 @@
         <v>0.78999999999999915</v>
       </c>
       <c r="H160" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I160">
         <v>69.989999999999995</v>
@@ -8966,10 +8966,10 @@
     </row>
     <row r="161" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B161" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C161">
         <v>1.99</v>
@@ -8987,7 +8987,7 @@
         <v>0.39999999999999858</v>
       </c>
       <c r="H161" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I161">
         <v>70.88</v>
@@ -9016,10 +9016,10 @@
     </row>
     <row r="162" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B162" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C162">
         <v>2.04</v>
@@ -9037,7 +9037,7 @@
         <v>0.32999999999999829</v>
       </c>
       <c r="H162" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I162">
         <v>69.44</v>
@@ -9069,10 +9069,10 @@
     </row>
     <row r="163" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B163" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C163">
         <v>1.99</v>
@@ -9090,7 +9090,7 @@
         <v>0.48000000000000398</v>
       </c>
       <c r="H163" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I163">
         <v>69.260000000000005</v>
@@ -9119,10 +9119,10 @@
     </row>
     <row r="164" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B164" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C164">
         <v>2.0099999999999998</v>
@@ -9140,7 +9140,7 @@
         <v>0.48999999999999488</v>
       </c>
       <c r="H164" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I164">
         <v>69.77</v>
@@ -9169,10 +9169,10 @@
     </row>
     <row r="165" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B165" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C165">
         <v>2.0099999999999998</v>
@@ -9190,7 +9190,7 @@
         <v>0.95000000000000284</v>
       </c>
       <c r="H165" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I165">
         <v>69.77</v>
@@ -9219,10 +9219,10 @@
     </row>
     <row r="166" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B166" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C166">
         <v>1.96</v>
@@ -9240,7 +9240,7 @@
         <v>0.46000000000000085</v>
       </c>
       <c r="H166" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I166">
         <v>70</v>
@@ -9269,10 +9269,10 @@
     </row>
     <row r="167" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B167" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C167">
         <v>2</v>
@@ -9290,7 +9290,7 @@
         <v>0.24000000000000199</v>
       </c>
       <c r="H167" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I167">
         <v>71.319999999999993</v>
@@ -9319,10 +9319,10 @@
     </row>
     <row r="168" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B168" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C168">
         <v>2</v>
@@ -9340,7 +9340,7 @@
         <v>0.23000000000000398</v>
       </c>
       <c r="H168" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I168">
         <v>69.13</v>
@@ -9369,10 +9369,10 @@
     </row>
     <row r="169" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B169" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C169">
         <v>1.97</v>
@@ -9390,7 +9390,7 @@
         <v>0.57000000000000028</v>
       </c>
       <c r="H169" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I169">
         <v>71.37</v>
@@ -9419,10 +9419,10 @@
     </row>
     <row r="170" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B170" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C170">
         <v>2.0299999999999998</v>
@@ -9440,7 +9440,7 @@
         <v>0.96000000000000085</v>
       </c>
       <c r="H170" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I170">
         <v>70.010000000000005</v>
@@ -9469,10 +9469,10 @@
     </row>
     <row r="171" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B171" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C171">
         <v>1.99</v>
@@ -9490,7 +9490,7 @@
         <v>0.60000000000000142</v>
       </c>
       <c r="H171" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I171">
         <v>70.19</v>
@@ -9519,10 +9519,10 @@
     </row>
     <row r="172" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B172" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C172">
         <v>1.98</v>
@@ -9540,7 +9540,7 @@
         <v>0.16000000000000369</v>
       </c>
       <c r="H172" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I172">
         <v>71.08</v>
@@ -9569,10 +9569,10 @@
     </row>
     <row r="173" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B173" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C173">
         <v>2.04</v>
@@ -9590,7 +9590,7 @@
         <v>0.13000000000000256</v>
       </c>
       <c r="H173" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I173">
         <v>70.84</v>
@@ -9619,10 +9619,10 @@
     </row>
     <row r="174" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B174" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C174">
         <v>2.02</v>
@@ -9640,7 +9640,7 @@
         <v>0.37999999999999545</v>
       </c>
       <c r="H174" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I174">
         <v>70.58</v>
@@ -9669,10 +9669,10 @@
     </row>
     <row r="175" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B175" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C175">
         <v>2</v>
@@ -9690,7 +9690,7 @@
         <v>0.26999999999999602</v>
       </c>
       <c r="H175" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I175">
         <v>70.48</v>
@@ -9719,10 +9719,10 @@
     </row>
     <row r="176" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B176" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C176">
         <v>2.02</v>
@@ -9740,7 +9740,7 @@
         <v>0.19999999999999574</v>
       </c>
       <c r="H176" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I176">
         <v>69.23</v>
@@ -9769,10 +9769,10 @@
     </row>
     <row r="177" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B177" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C177">
         <v>2.02</v>
@@ -9790,7 +9790,7 @@
         <v>0.51999999999999602</v>
       </c>
       <c r="H177" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I177">
         <v>71.05</v>
@@ -9819,10 +9819,10 @@
     </row>
     <row r="178" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B178" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C178">
         <v>2.0099999999999998</v>
@@ -9840,7 +9840,7 @@
         <v>0.55999999999999517</v>
       </c>
       <c r="H178" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I178">
         <v>69.099999999999994</v>
@@ -9869,10 +9869,10 @@
     </row>
     <row r="179" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B179" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C179">
         <v>2.0499999999999998</v>
@@ -9890,7 +9890,7 @@
         <v>0.93999999999999773</v>
       </c>
       <c r="H179" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I179">
         <v>68.739999999999995</v>
@@ -9919,10 +9919,10 @@
     </row>
     <row r="180" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B180" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C180">
         <v>2.0499999999999998</v>
@@ -9940,7 +9940,7 @@
         <v>0.3300000000000054</v>
       </c>
       <c r="H180" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I180">
         <v>71.28</v>
@@ -9969,10 +9969,10 @@
     </row>
     <row r="181" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B181" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C181">
         <v>1.98</v>
@@ -9990,7 +9990,7 @@
         <v>0.16000000000000369</v>
       </c>
       <c r="H181" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I181">
         <v>70.16</v>
@@ -10019,10 +10019,10 @@
     </row>
     <row r="182" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B182" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C182">
         <v>2.0299999999999998</v>
@@ -10040,7 +10040,7 @@
         <v>0.35999999999999943</v>
       </c>
       <c r="H182" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I182">
         <v>70.27</v>
@@ -10069,10 +10069,10 @@
     </row>
     <row r="183" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B183" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C183">
         <v>1.97</v>
@@ -10090,7 +10090,7 @@
         <v>0.20000000000000284</v>
       </c>
       <c r="H183" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I183">
         <v>71.19</v>
@@ -10119,10 +10119,10 @@
     </row>
     <row r="184" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B184" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C184">
         <v>2.0499999999999998</v>
@@ -10140,7 +10140,7 @@
         <v>0.34000000000000341</v>
       </c>
       <c r="H184" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I184">
         <v>68.59</v>
@@ -10169,10 +10169,10 @@
     </row>
     <row r="185" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B185" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C185">
         <v>1.98</v>
@@ -10190,7 +10190,7 @@
         <v>0.34999999999999432</v>
       </c>
       <c r="H185" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I185">
         <v>70</v>
@@ -10219,10 +10219,10 @@
     </row>
     <row r="186" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B186" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C186">
         <v>2.0099999999999998</v>
@@ -10240,7 +10240,7 @@
         <v>0.64000000000000057</v>
       </c>
       <c r="H186" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I186">
         <v>70.11</v>
@@ -10269,10 +10269,10 @@
     </row>
     <row r="187" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B187" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C187">
         <v>1.97</v>
@@ -10290,7 +10290,7 @@
         <v>0.17000000000000171</v>
       </c>
       <c r="H187" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I187">
         <v>69.67</v>
@@ -10319,10 +10319,10 @@
     </row>
     <row r="188" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B188" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C188">
         <v>2.02</v>
@@ -10340,7 +10340,7 @@
         <v>0.26000000000000512</v>
       </c>
       <c r="H188" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I188">
         <v>69.97</v>
@@ -10369,10 +10369,10 @@
     </row>
     <row r="189" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B189" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C189">
         <v>1.98</v>
@@ -10390,7 +10390,7 @@
         <v>0.59000000000000341</v>
       </c>
       <c r="H189" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I189">
         <v>69.09</v>
@@ -10419,10 +10419,10 @@
     </row>
     <row r="190" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B190" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C190">
         <v>2.0099999999999998</v>
@@ -10440,7 +10440,7 @@
         <v>0.42999999999999972</v>
       </c>
       <c r="H190" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I190">
         <v>70.44</v>
@@ -10469,10 +10469,10 @@
     </row>
     <row r="191" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B191" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C191">
         <v>1.97</v>
@@ -10490,7 +10490,7 @@
         <v>0.12000000000000455</v>
       </c>
       <c r="H191" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I191">
         <v>70.900000000000006</v>
@@ -10519,10 +10519,10 @@
     </row>
     <row r="192" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B192" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C192">
         <v>1.97</v>
@@ -10540,7 +10540,7 @@
         <v>0.47000000000000597</v>
       </c>
       <c r="H192" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I192">
         <v>68.87</v>
@@ -10569,10 +10569,10 @@
     </row>
     <row r="193" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B193" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C193">
         <v>2.0299999999999998</v>
@@ -10590,7 +10590,7 @@
         <v>0.60999999999999943</v>
       </c>
       <c r="H193" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I193">
         <v>68.56</v>
@@ -10619,10 +10619,10 @@
     </row>
     <row r="194" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B194" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C194">
         <v>2.04</v>
@@ -10640,7 +10640,7 @@
         <v>0.39000000000000057</v>
       </c>
       <c r="H194" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I194">
         <v>68.72</v>
@@ -10669,10 +10669,10 @@
     </row>
     <row r="195" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B195" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C195">
         <v>2.04</v>
@@ -10690,7 +10690,7 @@
         <v>0.21999999999999886</v>
       </c>
       <c r="H195" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I195">
         <v>70.040000000000006</v>
@@ -10719,10 +10719,10 @@
     </row>
     <row r="196" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B196" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C196">
         <v>2</v>
@@ -10740,7 +10740,7 @@
         <v>0.52000000000000313</v>
       </c>
       <c r="H196" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I196">
         <v>68.61</v>
@@ -10769,10 +10769,10 @@
     </row>
     <row r="197" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B197" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C197">
         <v>2</v>
@@ -10790,7 +10790,7 @@
         <v>0.60999999999999943</v>
       </c>
       <c r="H197" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I197">
         <v>69.69</v>
@@ -10819,10 +10819,10 @@
     </row>
     <row r="198" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B198" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C198">
         <v>2.02</v>
@@ -10840,7 +10840,7 @@
         <v>0.28999999999999915</v>
       </c>
       <c r="H198" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I198">
         <v>70.069999999999993</v>
@@ -10869,10 +10869,10 @@
     </row>
     <row r="199" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B199" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C199">
         <v>2.04</v>
@@ -10890,7 +10890,7 @@
         <v>0.67000000000000171</v>
       </c>
       <c r="H199" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I199">
         <v>70.069999999999993</v>
@@ -10919,10 +10919,10 @@
     </row>
     <row r="200" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B200" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C200">
         <v>2.0099999999999998</v>
@@ -10940,7 +10940,7 @@
         <v>0.62999999999999545</v>
       </c>
       <c r="H200" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I200">
         <v>73.900000000000006</v>
@@ -10969,10 +10969,10 @@
     </row>
     <row r="201" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B201" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C201">
         <v>1.99</v>
@@ -10990,7 +10990,7 @@
         <v>0.68999999999999773</v>
       </c>
       <c r="H201" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I201">
         <v>71.209999999999994</v>
@@ -11019,10 +11019,10 @@
     </row>
     <row r="202" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B202" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C202">
         <v>1.98</v>
@@ -11040,7 +11040,7 @@
         <v>0.26999999999999602</v>
       </c>
       <c r="H202" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I202">
         <v>70.34</v>
@@ -11069,10 +11069,10 @@
     </row>
     <row r="203" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B203" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C203">
         <v>2.02</v>
@@ -11090,7 +11090,7 @@
         <v>0.79999999999999716</v>
       </c>
       <c r="H203" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I203">
         <v>68.37</v>
@@ -11119,10 +11119,10 @@
     </row>
     <row r="204" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B204" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C204">
         <v>2.04</v>
@@ -11140,7 +11140,7 @@
         <v>0.40999999999999659</v>
       </c>
       <c r="H204" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I204">
         <v>69.569999999999993</v>
@@ -11169,10 +11169,10 @@
     </row>
     <row r="205" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B205" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C205">
         <v>2.04</v>
@@ -11190,7 +11190,7 @@
         <v>0.40000000000000568</v>
       </c>
       <c r="H205" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I205">
         <v>70.290000000000006</v>
@@ -11219,10 +11219,10 @@
     </row>
     <row r="206" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B206" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C206">
         <v>2.0099999999999998</v>
@@ -11240,7 +11240,7 @@
         <v>0.59000000000000341</v>
       </c>
       <c r="H206" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I206">
         <v>67.95</v>
@@ -11269,10 +11269,10 @@
     </row>
     <row r="207" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B207" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C207">
         <v>2.02</v>
@@ -11290,7 +11290,7 @@
         <v>0.29000000000000625</v>
       </c>
       <c r="H207" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I207">
         <v>69.849999999999994</v>
@@ -11319,10 +11319,10 @@
     </row>
     <row r="208" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B208" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C208">
         <v>2.0299999999999998</v>
@@ -11340,7 +11340,7 @@
         <v>0.69999999999998863</v>
       </c>
       <c r="H208" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I208">
         <v>69.819999999999993</v>
@@ -11369,10 +11369,10 @@
     </row>
     <row r="209" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B209" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C209">
         <v>2.0299999999999998</v>
@@ -11390,7 +11390,7 @@
         <v>0.37000000000000455</v>
       </c>
       <c r="H209" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I209">
         <v>70.58</v>
@@ -11419,10 +11419,10 @@
     </row>
     <row r="210" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B210" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C210">
         <v>2.0099999999999998</v>
@@ -11440,7 +11440,7 @@
         <v>0.34999999999999432</v>
       </c>
       <c r="H210" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I210">
         <v>68.94</v>
@@ -11469,10 +11469,10 @@
     </row>
     <row r="211" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B211" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C211">
         <v>2.04</v>
@@ -11490,7 +11490,7 @@
         <v>0.51000000000000512</v>
       </c>
       <c r="H211" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I211">
         <v>69.900000000000006</v>
@@ -11519,10 +11519,10 @@
     </row>
     <row r="212" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B212" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C212">
         <v>2.0099999999999998</v>
@@ -11540,7 +11540,7 @@
         <v>0.98000000000000398</v>
       </c>
       <c r="H212" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I212">
         <v>71.03</v>
@@ -11569,10 +11569,10 @@
     </row>
     <row r="213" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B213" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C213">
         <v>1.97</v>
@@ -11590,7 +11590,7 @@
         <v>1.8100000000000023</v>
       </c>
       <c r="H213" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I213">
         <v>70.98</v>
@@ -11619,10 +11619,10 @@
     </row>
     <row r="214" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B214" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C214">
         <v>2.04</v>
@@ -11640,7 +11640,7 @@
         <v>0.73000000000000398</v>
       </c>
       <c r="H214" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I214">
         <v>71.31</v>
@@ -11669,10 +11669,10 @@
     </row>
     <row r="215" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B215" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C215">
         <v>2.02</v>
@@ -11690,7 +11690,7 @@
         <v>0.28999999999999204</v>
       </c>
       <c r="H215" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I215">
         <v>70.709999999999994</v>
@@ -11719,10 +11719,10 @@
     </row>
     <row r="216" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B216" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C216">
         <v>2.02</v>
@@ -11740,7 +11740,7 @@
         <v>-1.0600000000000023</v>
       </c>
       <c r="H216" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I216">
         <v>68.64</v>
@@ -11769,10 +11769,10 @@
     </row>
     <row r="217" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B217" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C217">
         <v>2.04</v>
@@ -11790,7 +11790,7 @@
         <v>0.34999999999999432</v>
       </c>
       <c r="H217" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I217">
         <v>69.08</v>
@@ -11819,10 +11819,10 @@
     </row>
     <row r="218" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B218" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C218">
         <v>2.02</v>
@@ -11840,7 +11840,7 @@
         <v>0.26999999999999602</v>
       </c>
       <c r="H218" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I218">
         <v>70.12</v>
@@ -11869,10 +11869,10 @@
     </row>
     <row r="219" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B219" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C219">
         <v>2</v>
@@ -11890,7 +11890,7 @@
         <v>0.50999999999999091</v>
       </c>
       <c r="H219" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I219">
         <v>69.72</v>
@@ -11919,10 +11919,10 @@
     </row>
     <row r="220" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B220" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C220">
         <v>2</v>
@@ -11940,7 +11940,7 @@
         <v>0.31000000000000227</v>
       </c>
       <c r="H220" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I220">
         <v>71.599999999999994</v>
@@ -11969,10 +11969,10 @@
     </row>
     <row r="221" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B221" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C221">
         <v>1.98</v>
@@ -11990,7 +11990,7 @@
         <v>0.46999999999999886</v>
       </c>
       <c r="H221" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I221">
         <v>69.11</v>
@@ -12019,10 +12019,10 @@
     </row>
     <row r="222" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B222" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C222">
         <v>2.0099999999999998</v>
@@ -12040,7 +12040,7 @@
         <v>0.17999999999999261</v>
       </c>
       <c r="H222" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I222">
         <v>70.56</v>
@@ -12069,10 +12069,10 @@
     </row>
     <row r="223" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B223" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C223">
         <v>2.04</v>
@@ -12090,7 +12090,7 @@
         <v>0.82999999999999829</v>
       </c>
       <c r="H223" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I223">
         <v>70.900000000000006</v>
@@ -12119,10 +12119,10 @@
     </row>
     <row r="224" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B224" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C224">
         <v>2</v>
@@ -12140,7 +12140,7 @@
         <v>0.55000000000001137</v>
       </c>
       <c r="H224" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I224">
         <v>69.510000000000005</v>
@@ -12169,10 +12169,10 @@
     </row>
     <row r="225" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B225" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C225">
         <v>2</v>
@@ -12190,7 +12190,7 @@
         <v>0.25</v>
       </c>
       <c r="H225" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I225">
         <v>69.8</v>
@@ -12219,10 +12219,10 @@
     </row>
     <row r="226" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B226" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C226">
         <v>2.04</v>
@@ -12240,7 +12240,7 @@
         <v>0.43999999999999773</v>
       </c>
       <c r="H226" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I226">
         <v>70.739999999999995</v>
@@ -12269,10 +12269,10 @@
     </row>
     <row r="227" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B227" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C227">
         <v>2.0499999999999998</v>
@@ -12290,7 +12290,7 @@
         <v>0.36000000000001364</v>
       </c>
       <c r="H227" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I227">
         <v>70.06</v>
@@ -12319,10 +12319,10 @@
     </row>
     <row r="228" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B228" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C228">
         <v>2.02</v>
@@ -12340,7 +12340,7 @@
         <v>0.56000000000000227</v>
       </c>
       <c r="H228" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I228">
         <v>72.05</v>
@@ -12369,10 +12369,10 @@
     </row>
     <row r="229" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B229" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C229">
         <v>1.99</v>
@@ -12390,7 +12390,7 @@
         <v>0.46000000000000796</v>
       </c>
       <c r="H229" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I229">
         <v>69.650000000000006</v>
@@ -12419,10 +12419,10 @@
     </row>
     <row r="230" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B230" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C230">
         <v>2.0299999999999998</v>
@@ -12440,7 +12440,7 @@
         <v>0.46000000000000796</v>
       </c>
       <c r="H230" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I230">
         <v>67.91</v>
@@ -12469,10 +12469,10 @@
     </row>
     <row r="231" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B231" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C231">
         <v>2</v>
@@ -12490,7 +12490,7 @@
         <v>0.57000000000000739</v>
       </c>
       <c r="H231" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I231">
         <v>71.38</v>
@@ -12519,10 +12519,10 @@
     </row>
     <row r="232" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B232" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C232">
         <v>1.96</v>
@@ -12540,7 +12540,7 @@
         <v>0.60999999999999943</v>
       </c>
       <c r="H232" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I232">
         <v>69.73</v>
@@ -12569,10 +12569,10 @@
     </row>
     <row r="233" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B233" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C233">
         <v>2</v>
@@ -12590,7 +12590,7 @@
         <v>0.48000000000000398</v>
       </c>
       <c r="H233" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I233">
         <v>71.459999999999994</v>
@@ -12619,10 +12619,10 @@
     </row>
     <row r="234" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B234" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C234">
         <v>2.0499999999999998</v>
@@ -12640,7 +12640,7 @@
         <v>0.21999999999999886</v>
       </c>
       <c r="H234" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I234">
         <v>70.47</v>
@@ -12669,10 +12669,10 @@
     </row>
     <row r="235" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B235" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C235">
         <v>1.97</v>
@@ -12690,7 +12690,7 @@
         <v>0.31000000000000227</v>
       </c>
       <c r="H235" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I235">
         <v>69.3</v>
@@ -12719,10 +12719,10 @@
     </row>
     <row r="236" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B236" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C236">
         <v>2.02</v>
@@ -12740,7 +12740,7 @@
         <v>0.32999999999999829</v>
       </c>
       <c r="H236" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I236">
         <v>70.010000000000005</v>
@@ -12769,10 +12769,10 @@
     </row>
     <row r="237" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B237" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C237">
         <v>1.95</v>
@@ -12790,7 +12790,7 @@
         <v>0.76000000000000512</v>
       </c>
       <c r="H237" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I237">
         <v>69.06</v>
@@ -12819,10 +12819,10 @@
     </row>
     <row r="238" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B238" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C238">
         <v>2.0299999999999998</v>
@@ -12840,7 +12840,7 @@
         <v>0.80000000000001137</v>
       </c>
       <c r="H238" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I238">
         <v>68.47</v>
@@ -12869,10 +12869,10 @@
     </row>
     <row r="239" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B239" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C239">
         <v>2.04</v>
@@ -12890,7 +12890,7 @@
         <v>0.34999999999999432</v>
       </c>
       <c r="H239" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I239">
         <v>69.739999999999995</v>
@@ -12919,10 +12919,10 @@
     </row>
     <row r="240" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B240" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C240">
         <v>2.0299999999999998</v>
@@ -12940,7 +12940,7 @@
         <v>9.9999999999994316E-2</v>
       </c>
       <c r="H240" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I240">
         <v>70.84</v>
@@ -12969,10 +12969,10 @@
     </row>
     <row r="241" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B241" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C241">
         <v>1.97</v>
@@ -12990,7 +12990,7 @@
         <v>0.23000000000000398</v>
       </c>
       <c r="H241" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I241">
         <v>70.459999999999994</v>
